--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Abertura: 3 minutos antes do primeiro paciente. Fechamento: 10 minutos depois do último. Na sexta, o sócio da semana olha o Painel junto com o caixa (09).</t>
+          <t>É o roteiro diário da recepção, fora dos 30 minutos semanais dos sócios (planilha 03): abertura, 3 minutos antes do primeiro paciente; fechamento, 10 minutos depois do último — são 13 minutos por dia. O fechamento inclui lançar o caixa do dia na planilha 09; na sexta a sócia só confere os cinco fechamentos da semana (rotina de sexta da 03).</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Dias úteis de 01/07 a 11/09/2026, preenchidos pela recepção. Sexta-feira 11/09 tem itens de fechamento em branco: é o que o Painel aponta na segunda.</t>
+          <t>Dias úteis de 01/06 a 11/09/2026, preenchidos pela recepção. Sexta-feira 11/09 tem itens de fechamento em branco: é o que o Painel aponta na segunda.</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;")</f>
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>IFERROR(COUNTIFS(Checklist!$AB$5:$AB$304,"&lt;="&amp;Config!$B$6,Checklist!$AB$5:$AB$304,"&gt;0",Checklist!$V$5:$V$304,0)/MIN(Config!$B$6,COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;")),"")</f>
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="16">
@@ -1033,12 +1033,12 @@
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="17">
         <f>COUNTIFS(Checklist!$X$5:$X$304,"&gt;0")</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="18">
         <f>SUM(Checklist!$X$5:$X$304)</f>
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J5" s="14" t="n"/>
     </row>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B10" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46260.0</v>
+        <v>46266.0</v>
       </c>
       <c r="C10" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="D10" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1119,11 +1119,11 @@
       </c>
       <c r="E10" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F10" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H10" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,1)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,1),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Faltas e cancelamentos de ontem registrados na agenda; Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Situação de cada horário marcada (realizado, falta, cancelado)</v>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Fechamento do dia lançado no Caixa (09); Guias do dia conferidas e guardadas para o lote (13)</v>
       </c>
       <c r="I10" s="22" t="n"/>
       <c r="J10" s="23" t="n"/>
@@ -1142,11 +1142,11 @@
       </c>
       <c r="B11" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46276.0</v>
+        <v>46231.0</v>
       </c>
       <c r="C11" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Sexta</v>
+        <v>Terça</v>
       </c>
       <c r="D11" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E11" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1162,11 +1162,11 @@
       </c>
       <c r="G11" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,2)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,2),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Fechamento do dia lançado no Caixa (09); Guias do dia conferidas e guardadas para o lote (13)</v>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Situação de cada horário marcada (realizado, falta, cancelado)</v>
       </c>
       <c r="I11" s="22" t="n"/>
       <c r="J11" s="23" t="n"/>
@@ -1177,11 +1177,11 @@
       </c>
       <c r="B12" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46268.0</v>
+        <v>46276.0</v>
       </c>
       <c r="C12" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Quinta</v>
+        <v>Sexta</v>
       </c>
       <c r="D12" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1189,11 +1189,11 @@
       </c>
       <c r="E12" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F12" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="G12" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H12" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,3)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,3),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Retornos e exames do dia agendados</v>
+        <v>Troco e maquininha conferidos; Guias do dia conferidas e guardadas para o lote (13)</v>
       </c>
       <c r="I12" s="22" t="n"/>
       <c r="J12" s="23" t="n"/>
@@ -1212,11 +1212,11 @@
       </c>
       <c r="B13" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46252.0</v>
+        <v>46275.0</v>
       </c>
       <c r="C13" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Terça</v>
+        <v>Quinta</v>
       </c>
       <c r="D13" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="E13" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F13" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="G13" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H13" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,4)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,4),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Situação de cada horário marcada (realizado, falta, cancelado)</v>
+        <v>Guias e autorizações de convênio do dia separadas; Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="I13" s="22" t="n"/>
       <c r="J13" s="23" t="n"/>
@@ -1247,11 +1247,11 @@
       </c>
       <c r="B14" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,5)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46239.0</v>
+        <v>46268.0</v>
       </c>
       <c r="C14" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,5)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Quarta</v>
+        <v>Quinta</v>
       </c>
       <c r="D14" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,5)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="H14" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,5)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,5),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Troco e maquininha conferidos; Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Agenda de amanhã revisada e confirmações enviadas</v>
       </c>
       <c r="I14" s="22" t="n"/>
       <c r="J14" s="23" t="n"/>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="B15" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46227.0</v>
+        <v>46258.0</v>
       </c>
       <c r="C15" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Sexta</v>
+        <v>Segunda</v>
       </c>
       <c r="D15" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1294,11 +1294,11 @@
       </c>
       <c r="E15" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="F15" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G15" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H15" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,6)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,6),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Troco e maquininha conferidos; Orçamentos sem resposta revisados (lista da 15)</v>
+        <v>Fechamento do dia lançado no Caixa (09); Situação de cada horário marcada (realizado, falta, cancelado)</v>
       </c>
       <c r="I15" s="22" t="n"/>
       <c r="J15" s="23" t="n"/>
@@ -1317,11 +1317,11 @@
       </c>
       <c r="B16" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46216.0</v>
+        <v>46255.0</v>
       </c>
       <c r="C16" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="D16" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="E16" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F16" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="G16" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="H16" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,7)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,7),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Fechamento do dia lançado no Caixa (09)</v>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="I16" s="22" t="n"/>
       <c r="J16" s="23" t="n"/>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="B17" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,8)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46275.0</v>
+        <v>46239.0</v>
       </c>
       <c r="C17" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,8)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="D17" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,8)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1368,15 +1368,15 @@
       </c>
       <c r="F17" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,8)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.833333333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G17" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,8)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,8)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,8),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Fechamento do dia lançado no Caixa (09)</v>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Retornos e exames do dia agendados</v>
       </c>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="23" t="n"/>
@@ -1387,11 +1387,11 @@
       </c>
       <c r="B18" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46274.0</v>
+        <v>46223.0</v>
       </c>
       <c r="C18" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Quarta</v>
+        <v>Segunda</v>
       </c>
       <c r="D18" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1399,19 +1399,19 @@
       </c>
       <c r="E18" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F18" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G18" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,9)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,9),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Guias e autorizações de convênio do dia separadas</v>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Situação de cada horário marcada (realizado, falta, cancelado)</v>
       </c>
       <c r="I18" s="22" t="n"/>
       <c r="J18" s="23" t="n"/>
@@ -1422,11 +1422,11 @@
       </c>
       <c r="B19" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46265.0</v>
+        <v>46210.0</v>
       </c>
       <c r="C19" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Segunda</v>
+        <v>Terça</v>
       </c>
       <c r="D19" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E19" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F19" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="G19" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,10)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,10),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Fechamento do dia lançado no Caixa (09)</v>
+        <v>Troco e maquininha conferidos; Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
       </c>
       <c r="I19" s="22" t="n"/>
       <c r="J19" s="23" t="n"/>
@@ -1457,11 +1457,11 @@
       </c>
       <c r="B20" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46262.0</v>
+        <v>46198.0</v>
       </c>
       <c r="C20" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="D20" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E20" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$T$5:$T$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1477,11 +1477,11 @@
       </c>
       <c r="G20" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,11)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,11),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
+        <v>Troco e maquininha conferidos; Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
       </c>
       <c r="I20" s="22" t="n"/>
       <c r="J20" s="23" t="n"/>
@@ -1492,11 +1492,11 @@
       </c>
       <c r="B21" s="25">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,12)&gt;0,IF(INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$A$5:$A$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>46261.0</v>
+        <v>46185.0</v>
       </c>
       <c r="C21" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,12)&gt;0,IF(INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$B$5:$B$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Quinta</v>
+        <v>Sexta</v>
       </c>
       <c r="D21" s="24" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,12)&gt;0,IF(INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$C$5:$C$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))),""),"")</f>
@@ -1508,15 +1508,15 @@
       </c>
       <c r="F21" s="26">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,12)&gt;0,IF(INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$U$5:$U$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>0.833333333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G21" s="24">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,12)&gt;0,IF(INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$X$5:$X$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="27" t="str">
         <f>IFERROR(IF(LARGE(Checklist!$Z$5:$Z$304,12)&gt;0,IF(INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))="","",INDEX(Checklist!$Y$5:$Y$304,MATCH(LARGE(Checklist!$Z$5:$Z$304,12),Checklist!$Z$5:$Z$304,0))),""),"")</f>
-        <v>Fechamento do dia lançado no Caixa (09)</v>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="I21" s="22" t="n"/>
       <c r="J21" s="23" t="n"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D26" s="24">
         <f>IF(Config!$B$10="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$D$5:$D$304,"Sim"))</f>
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E26" s="24">
         <f>IF(Config!$B$10="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$D$5:$D$304,"N/A"))</f>
@@ -1605,11 +1605,11 @@
       <c r="G26" s="24" t="n"/>
       <c r="H26" s="24">
         <f>IF(Config!$D$10="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$L$5:$L$304,"&lt;&gt;Sim",Checklist!$L$5:$L$304,"&lt;&gt;N/A"))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I26" s="24">
         <f>IF(Config!$D$10="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$L$5:$L$304,"Sim"))</f>
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="J26" s="24">
         <f>IF(Config!$D$10="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$L$5:$L$304,"N/A"))</f>
@@ -1624,11 +1624,11 @@
       <c r="B27" s="24" t="n"/>
       <c r="C27" s="24">
         <f>IF(Config!$B$11="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$E$5:$E$304,"&lt;&gt;Sim",Checklist!$E$5:$E$304,"&lt;&gt;N/A"))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" s="24">
         <f>IF(Config!$B$11="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$E$5:$E$304,"Sim"))</f>
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E27" s="24">
         <f>IF(Config!$B$11="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$E$5:$E$304,"N/A"))</f>
@@ -1641,11 +1641,11 @@
       <c r="G27" s="24" t="n"/>
       <c r="H27" s="24">
         <f>IF(Config!$D$11="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$M$5:$M$304,"&lt;&gt;Sim",Checklist!$M$5:$M$304,"&lt;&gt;N/A"))</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I27" s="24">
         <f>IF(Config!$D$11="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$M$5:$M$304,"Sim"))</f>
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="J27" s="24">
         <f>IF(Config!$D$11="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$M$5:$M$304,"N/A"))</f>
@@ -1660,11 +1660,11 @@
       <c r="B28" s="24" t="n"/>
       <c r="C28" s="24">
         <f>IF(Config!$B$12="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$F$5:$F$304,"&lt;&gt;Sim",Checklist!$F$5:$F$304,"&lt;&gt;N/A"))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="24">
         <f>IF(Config!$B$12="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$F$5:$F$304,"Sim"))</f>
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E28" s="24">
         <f>IF(Config!$B$12="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$F$5:$F$304,"N/A"))</f>
@@ -1677,11 +1677,11 @@
       <c r="G28" s="24" t="n"/>
       <c r="H28" s="24">
         <f>IF(Config!$D$12="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$N$5:$N$304,"&lt;&gt;Sim",Checklist!$N$5:$N$304,"&lt;&gt;N/A"))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" s="24">
         <f>IF(Config!$D$12="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$N$5:$N$304,"Sim"))</f>
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="J28" s="24">
         <f>IF(Config!$D$12="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$N$5:$N$304,"N/A"))</f>
@@ -1696,11 +1696,11 @@
       <c r="B29" s="24" t="n"/>
       <c r="C29" s="24">
         <f>IF(Config!$B$13="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$G$5:$G$304,"&lt;&gt;Sim",Checklist!$G$5:$G$304,"&lt;&gt;N/A"))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="24">
         <f>IF(Config!$B$13="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$G$5:$G$304,"Sim"))</f>
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E29" s="24">
         <f>IF(Config!$B$13="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$G$5:$G$304,"N/A"))</f>
@@ -1713,11 +1713,11 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24">
         <f>IF(Config!$D$13="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$O$5:$O$304,"&lt;&gt;Sim",Checklist!$O$5:$O$304,"&lt;&gt;N/A"))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="24">
         <f>IF(Config!$D$13="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$O$5:$O$304,"Sim"))</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J29" s="24">
         <f>IF(Config!$D$13="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$O$5:$O$304,"N/A"))</f>
@@ -1732,11 +1732,11 @@
       <c r="B30" s="24" t="n"/>
       <c r="C30" s="24">
         <f>IF(Config!$B$14="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$H$5:$H$304,"&lt;&gt;Sim",Checklist!$H$5:$H$304,"&lt;&gt;N/A"))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="24">
         <f>IF(Config!$B$14="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$H$5:$H$304,"Sim"))</f>
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E30" s="24">
         <f>IF(Config!$B$14="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$H$5:$H$304,"N/A"))</f>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="I30" s="24">
         <f>IF(Config!$D$14="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$P$5:$P$304,"Sim"))</f>
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="J30" s="24">
         <f>IF(Config!$D$14="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$P$5:$P$304,"N/A"))</f>
@@ -1768,15 +1768,15 @@
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="24">
         <f>IF(Config!$B$15="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$I$5:$I$304,"&lt;&gt;Sim",Checklist!$I$5:$I$304,"&lt;&gt;N/A"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="24">
         <f>IF(Config!$B$15="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$I$5:$I$304,"Sim"))</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E31" s="24">
         <f>IF(Config!$B$15="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$I$5:$I$304,"N/A"))</f>
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F31" s="28" t="str">
         <f>IF(Config!$D$15="","",Config!$D$15)</f>
@@ -1785,11 +1785,11 @@
       <c r="G31" s="24" t="n"/>
       <c r="H31" s="24">
         <f>IF(Config!$D$15="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$Q$5:$Q$304,"&lt;&gt;Sim",Checklist!$Q$5:$Q$304,"&lt;&gt;N/A"))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="24">
         <f>IF(Config!$D$15="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$Q$5:$Q$304,"Sim"))</f>
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J31" s="24">
         <f>IF(Config!$D$15="","",COUNTIFS(Checklist!$A$5:$A$304,"&lt;&gt;",Checklist!$Q$5:$Q$304,"N/A"))</f>
@@ -1919,23 +1919,23 @@
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A38)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D38" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A38,Checklist!$X$5:$X$304,"&gt;0")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" s="24">
         <f>SUMIFS(Checklist!$X$5:$X$304,Checklist!$B$5:$B$304,A38)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="26">
         <f>IF(C38=0,"",COUNTIFS(Checklist!$B$5:$B$304,A38,Checklist!$V$5:$V$304,0)/C38)</f>
-        <v>0.888888888888889</v>
+        <v>0.928571428571429</v>
       </c>
       <c r="G38" s="26">
         <f>IF(C38=0,"",COUNTIFS(Checklist!$B$5:$B$304,A38,Checklist!$W$5:$W$304,0)/C38)</f>
-        <v>0.555555555555556</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="39">
@@ -1947,23 +1947,23 @@
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A39)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D39" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A39,Checklist!$X$5:$X$304,"&gt;0")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E39" s="24">
         <f>SUMIFS(Checklist!$X$5:$X$304,Checklist!$B$5:$B$304,A39)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F39" s="26">
         <f>IF(C39=0,"",COUNTIFS(Checklist!$B$5:$B$304,A39,Checklist!$V$5:$V$304,0)/C39)</f>
-        <v>1</v>
+        <v>0.866666666666667</v>
       </c>
       <c r="G39" s="26">
         <f>IF(C39=0,"",COUNTIFS(Checklist!$B$5:$B$304,A39,Checklist!$W$5:$W$304,0)/C39)</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40">
@@ -1975,11 +1975,11 @@
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A40)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D40" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A40,Checklist!$X$5:$X$304,"&gt;0")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" s="24">
         <f>SUMIFS(Checklist!$X$5:$X$304,Checklist!$B$5:$B$304,A40)</f>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="F40" s="26">
         <f>IF(C40=0,"",COUNTIFS(Checklist!$B$5:$B$304,A40,Checklist!$V$5:$V$304,0)/C40)</f>
-        <v>0.727272727272727</v>
+        <v>0.866666666666667</v>
       </c>
       <c r="G40" s="26">
         <f>IF(C40=0,"",COUNTIFS(Checklist!$B$5:$B$304,A40,Checklist!$W$5:$W$304,0)/C40)</f>
-        <v>0.636363636363636</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -2003,7 +2003,7 @@
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A41)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D41" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A41,Checklist!$X$5:$X$304,"&gt;0")</f>
@@ -2011,15 +2011,15 @@
       </c>
       <c r="E41" s="24">
         <f>SUMIFS(Checklist!$X$5:$X$304,Checklist!$B$5:$B$304,A41)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" s="26">
         <f>IF(C41=0,"",COUNTIFS(Checklist!$B$5:$B$304,A41,Checklist!$V$5:$V$304,0)/C41)</f>
-        <v>0.818181818181818</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="G41" s="26">
         <f>IF(C41=0,"",COUNTIFS(Checklist!$B$5:$B$304,A41,Checklist!$W$5:$W$304,0)/C41)</f>
-        <v>0.545454545454545</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="42">
@@ -2031,23 +2031,23 @@
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A42)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D42" s="24">
         <f>COUNTIFS(Checklist!$B$5:$B$304,A42,Checklist!$X$5:$X$304,"&gt;0")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E42" s="24">
         <f>SUMIFS(Checklist!$X$5:$X$304,Checklist!$B$5:$B$304,A42)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F42" s="26">
         <f>IF(C42=0,"",COUNTIFS(Checklist!$B$5:$B$304,A42,Checklist!$V$5:$V$304,0)/C42)</f>
-        <v>0.727272727272727</v>
+        <v>0.8</v>
       </c>
       <c r="G42" s="26">
         <f>IF(C42=0,"",COUNTIFS(Checklist!$B$5:$B$304,A42,Checklist!$W$5:$W$304,0)/C42)</f>
-        <v>0.818181818181818</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -2587,11 +2587,11 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="24" t="str">
         <f>IF(A5="","",CHOOSE(WEEKDAY(A5,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Segunda</v>
       </c>
       <c r="C5" s="38" t="inlineStr">
         <is>
@@ -2696,16 +2696,16 @@
       </c>
       <c r="AB5" s="39">
         <f>IF(A5="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A5)+1)</f>
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="37" t="n">
-        <v>46205</v>
+        <v>46175</v>
       </c>
       <c r="B6" s="24" t="str">
         <f>IF(A6="","",CHOOSE(WEEKDAY(A6,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Terça</v>
       </c>
       <c r="C6" s="38" t="inlineStr">
         <is>
@@ -2810,16 +2810,16 @@
       </c>
       <c r="AB6" s="39">
         <f>IF(A6="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A6)+1)</f>
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="37" t="n">
-        <v>46206</v>
+        <v>46176</v>
       </c>
       <c r="B7" s="24" t="str">
         <f>IF(A7="","",CHOOSE(WEEKDAY(A7,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quarta</v>
       </c>
       <c r="C7" s="38" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="I7" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="38" t="n"/>
@@ -2924,16 +2924,16 @@
       </c>
       <c r="AB7" s="39">
         <f>IF(A7="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A7)+1)</f>
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n">
-        <v>46209</v>
+        <v>46178</v>
       </c>
       <c r="B8" s="24" t="str">
         <f>IF(A8="","",CHOOSE(WEEKDAY(A8,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="I8" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J8" s="38" t="n"/>
@@ -3038,16 +3038,16 @@
       </c>
       <c r="AB8" s="39">
         <f>IF(A8="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A8)+1)</f>
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="37" t="n">
-        <v>46210</v>
+        <v>46181</v>
       </c>
       <c r="B9" s="24" t="str">
         <f>IF(A9="","",CHOOSE(WEEKDAY(A9,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C9" s="38" t="inlineStr">
         <is>
@@ -3152,16 +3152,16 @@
       </c>
       <c r="AB9" s="39">
         <f>IF(A9="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A9)+1)</f>
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="37" t="n">
-        <v>46211</v>
+        <v>46182</v>
       </c>
       <c r="B10" s="24" t="str">
         <f>IF(A10="","",CHOOSE(WEEKDAY(A10,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
@@ -3266,16 +3266,16 @@
       </c>
       <c r="AB10" s="39">
         <f>IF(A10="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A10)+1)</f>
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="37" t="n">
-        <v>46212</v>
+        <v>46183</v>
       </c>
       <c r="B11" s="24" t="str">
         <f>IF(A11="","",CHOOSE(WEEKDAY(A11,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C11" s="38" t="inlineStr">
         <is>
@@ -3380,16 +3380,16 @@
       </c>
       <c r="AB11" s="39">
         <f>IF(A11="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A11)+1)</f>
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="37" t="n">
-        <v>46213</v>
+        <v>46184</v>
       </c>
       <c r="B12" s="24" t="str">
         <f>IF(A12="","",CHOOSE(WEEKDAY(A12,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C12" s="38" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I12" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J12" s="38" t="n"/>
@@ -3462,7 +3462,7 @@
       <c r="S12" s="38" t="n"/>
       <c r="T12" s="26">
         <f>IF(A12="","",IFERROR(COUNTIF(D12:K12,"Sim")/(Config!$B$19-COUNTIF(D12:K12,"N/A")),""))</f>
-        <v>0.833333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="U12" s="26">
         <f>IF(A12="","",IFERROR(COUNTIF(L12:S12,"Sim")/(Config!$D$19-COUNTIF(L12:S12,"N/A")),""))</f>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Z12" s="39">
         <f>IF(OR(A12="",X12=0),0,X12*100000+A12/100000)</f>
-        <v>100000.46213</v>
+        <v>100000.46184</v>
       </c>
       <c r="AA12" s="39" t="str">
         <f>IF(A12="","",IF(AND(Config!$B$10&lt;&gt;"",D12&lt;&gt;"Sim",D12&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E12&lt;&gt;"Sim",E12&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F12&lt;&gt;"Sim",F12&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G12&lt;&gt;"Sim",G12&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H12&lt;&gt;"Sim",H12&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I12&lt;&gt;"Sim",I12&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J12&lt;&gt;"Sim",J12&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K12&lt;&gt;"Sim",K12&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L12&lt;&gt;"Sim",L12&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M12&lt;&gt;"Sim",M12&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N12&lt;&gt;"Sim",N12&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O12&lt;&gt;"Sim",O12&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P12&lt;&gt;"Sim",P12&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q12&lt;&gt;"Sim",Q12&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R12&lt;&gt;"Sim",R12&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S12&lt;&gt;"Sim",S12&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -3494,16 +3494,16 @@
       </c>
       <c r="AB12" s="39">
         <f>IF(A12="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A12)+1)</f>
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="37" t="n">
-        <v>46216</v>
+        <v>46185</v>
       </c>
       <c r="B13" s="24" t="str">
         <f>IF(A13="","",CHOOSE(WEEKDAY(A13,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C13" s="38" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="I13" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J13" s="38" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="Z13" s="39">
         <f>IF(OR(A13="",X13=0),0,X13*100000+A13/100000)</f>
-        <v>200000.46216</v>
+        <v>200000.46185</v>
       </c>
       <c r="AA13" s="39" t="str">
         <f>IF(A13="","",IF(AND(Config!$B$10&lt;&gt;"",D13&lt;&gt;"Sim",D13&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E13&lt;&gt;"Sim",E13&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F13&lt;&gt;"Sim",F13&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G13&lt;&gt;"Sim",G13&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H13&lt;&gt;"Sim",H13&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I13&lt;&gt;"Sim",I13&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J13&lt;&gt;"Sim",J13&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K13&lt;&gt;"Sim",K13&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L13&lt;&gt;"Sim",L13&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M13&lt;&gt;"Sim",M13&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N13&lt;&gt;"Sim",N13&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O13&lt;&gt;"Sim",O13&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P13&lt;&gt;"Sim",P13&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q13&lt;&gt;"Sim",Q13&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R13&lt;&gt;"Sim",R13&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S13&lt;&gt;"Sim",S13&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -3608,16 +3608,16 @@
       </c>
       <c r="AB13" s="39">
         <f>IF(A13="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A13)+1)</f>
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="37" t="n">
-        <v>46217</v>
+        <v>46188</v>
       </c>
       <c r="B14" s="24" t="str">
         <f>IF(A14="","",CHOOSE(WEEKDAY(A14,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
@@ -3722,16 +3722,16 @@
       </c>
       <c r="AB14" s="39">
         <f>IF(A14="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A14)+1)</f>
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="37" t="n">
-        <v>46218</v>
+        <v>46189</v>
       </c>
       <c r="B15" s="24" t="str">
         <f>IF(A15="","",CHOOSE(WEEKDAY(A15,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C15" s="38" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="Z15" s="39">
         <f>IF(OR(A15="",X15=0),0,X15*100000+A15/100000)</f>
-        <v>100000.46218</v>
+        <v>100000.46189</v>
       </c>
       <c r="AA15" s="39" t="str">
         <f>IF(A15="","",IF(AND(Config!$B$10&lt;&gt;"",D15&lt;&gt;"Sim",D15&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E15&lt;&gt;"Sim",E15&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F15&lt;&gt;"Sim",F15&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G15&lt;&gt;"Sim",G15&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H15&lt;&gt;"Sim",H15&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I15&lt;&gt;"Sim",I15&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J15&lt;&gt;"Sim",J15&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K15&lt;&gt;"Sim",K15&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L15&lt;&gt;"Sim",L15&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M15&lt;&gt;"Sim",M15&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N15&lt;&gt;"Sim",N15&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O15&lt;&gt;"Sim",O15&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P15&lt;&gt;"Sim",P15&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q15&lt;&gt;"Sim",Q15&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R15&lt;&gt;"Sim",R15&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S15&lt;&gt;"Sim",S15&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -3836,16 +3836,16 @@
       </c>
       <c r="AB15" s="39">
         <f>IF(A15="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A15)+1)</f>
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="37" t="n">
-        <v>46219</v>
+        <v>46190</v>
       </c>
       <c r="B16" s="24" t="str">
         <f>IF(A16="","",CHOOSE(WEEKDAY(A16,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="Z16" s="39">
         <f>IF(OR(A16="",X16=0),0,X16*100000+A16/100000)</f>
-        <v>100000.46219</v>
+        <v>100000.4619</v>
       </c>
       <c r="AA16" s="39" t="str">
         <f>IF(A16="","",IF(AND(Config!$B$10&lt;&gt;"",D16&lt;&gt;"Sim",D16&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E16&lt;&gt;"Sim",E16&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F16&lt;&gt;"Sim",F16&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G16&lt;&gt;"Sim",G16&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H16&lt;&gt;"Sim",H16&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I16&lt;&gt;"Sim",I16&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J16&lt;&gt;"Sim",J16&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K16&lt;&gt;"Sim",K16&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L16&lt;&gt;"Sim",L16&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M16&lt;&gt;"Sim",M16&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N16&lt;&gt;"Sim",N16&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O16&lt;&gt;"Sim",O16&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P16&lt;&gt;"Sim",P16&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q16&lt;&gt;"Sim",Q16&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R16&lt;&gt;"Sim",R16&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S16&lt;&gt;"Sim",S16&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -3950,16 +3950,16 @@
       </c>
       <c r="AB16" s="39">
         <f>IF(A16="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A16)+1)</f>
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n">
-        <v>46220</v>
+        <v>46191</v>
       </c>
       <c r="B17" s="24" t="str">
         <f>IF(A17="","",CHOOSE(WEEKDAY(A17,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C17" s="38" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I17" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J17" s="38" t="n"/>
@@ -4064,16 +4064,16 @@
       </c>
       <c r="AB17" s="39">
         <f>IF(A17="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A17)+1)</f>
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n">
-        <v>46223</v>
+        <v>46192</v>
       </c>
       <c r="B18" s="24" t="str">
         <f>IF(A18="","",CHOOSE(WEEKDAY(A18,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="I18" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J18" s="38" t="n"/>
@@ -4178,16 +4178,16 @@
       </c>
       <c r="AB18" s="39">
         <f>IF(A18="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A18)+1)</f>
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n">
-        <v>46224</v>
+        <v>46195</v>
       </c>
       <c r="B19" s="24" t="str">
         <f>IF(A19="","",CHOOSE(WEEKDAY(A19,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C19" s="38" t="inlineStr">
         <is>
@@ -4292,16 +4292,16 @@
       </c>
       <c r="AB19" s="39">
         <f>IF(A19="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A19)+1)</f>
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="37" t="n">
-        <v>46225</v>
+        <v>46196</v>
       </c>
       <c r="B20" s="24" t="str">
         <f>IF(A20="","",CHOOSE(WEEKDAY(A20,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="Z20" s="39">
         <f>IF(OR(A20="",X20=0),0,X20*100000+A20/100000)</f>
-        <v>100000.46225</v>
+        <v>100000.46196</v>
       </c>
       <c r="AA20" s="39" t="str">
         <f>IF(A20="","",IF(AND(Config!$B$10&lt;&gt;"",D20&lt;&gt;"Sim",D20&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E20&lt;&gt;"Sim",E20&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F20&lt;&gt;"Sim",F20&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G20&lt;&gt;"Sim",G20&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H20&lt;&gt;"Sim",H20&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I20&lt;&gt;"Sim",I20&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J20&lt;&gt;"Sim",J20&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K20&lt;&gt;"Sim",K20&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L20&lt;&gt;"Sim",L20&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M20&lt;&gt;"Sim",M20&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N20&lt;&gt;"Sim",N20&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O20&lt;&gt;"Sim",O20&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P20&lt;&gt;"Sim",P20&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q20&lt;&gt;"Sim",Q20&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R20&lt;&gt;"Sim",R20&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S20&lt;&gt;"Sim",S20&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -4406,16 +4406,16 @@
       </c>
       <c r="AB20" s="39">
         <f>IF(A20="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A20)+1)</f>
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="37" t="n">
-        <v>46226</v>
+        <v>46197</v>
       </c>
       <c r="B21" s="24" t="str">
         <f>IF(A21="","",CHOOSE(WEEKDAY(A21,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C21" s="38" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z21" s="39">
         <f>IF(OR(A21="",X21=0),0,X21*100000+A21/100000)</f>
-        <v>100000.46226</v>
+        <v>100000.46197</v>
       </c>
       <c r="AA21" s="39" t="str">
         <f>IF(A21="","",IF(AND(Config!$B$10&lt;&gt;"",D21&lt;&gt;"Sim",D21&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E21&lt;&gt;"Sim",E21&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F21&lt;&gt;"Sim",F21&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G21&lt;&gt;"Sim",G21&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H21&lt;&gt;"Sim",H21&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I21&lt;&gt;"Sim",I21&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J21&lt;&gt;"Sim",J21&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K21&lt;&gt;"Sim",K21&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L21&lt;&gt;"Sim",L21&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M21&lt;&gt;"Sim",M21&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N21&lt;&gt;"Sim",N21&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O21&lt;&gt;"Sim",O21&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P21&lt;&gt;"Sim",P21&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q21&lt;&gt;"Sim",Q21&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R21&lt;&gt;"Sim",R21&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S21&lt;&gt;"Sim",S21&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -4520,16 +4520,16 @@
       </c>
       <c r="AB21" s="39">
         <f>IF(A21="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A21)+1)</f>
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="37" t="n">
-        <v>46227</v>
+        <v>46198</v>
       </c>
       <c r="B22" s="24" t="str">
         <f>IF(A22="","",CHOOSE(WEEKDAY(A22,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
@@ -4563,14 +4563,14 @@
       </c>
       <c r="I22" s="38" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J22" s="38" t="n"/>
       <c r="K22" s="38" t="n"/>
       <c r="L22" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="M22" s="38" t="inlineStr">
@@ -4602,19 +4602,19 @@
       <c r="S22" s="38" t="n"/>
       <c r="T22" s="26">
         <f>IF(A22="","",IFERROR(COUNTIF(D22:K22,"Sim")/(Config!$B$19-COUNTIF(D22:K22,"N/A")),""))</f>
-        <v>0.666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="U22" s="26">
         <f>IF(A22="","",IFERROR(COUNTIF(L22:S22,"Sim")/(Config!$D$19-COUNTIF(L22:S22,"N/A")),""))</f>
-        <v>1</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="V22" s="24">
         <f>IF(A22="","",MAX(0,Config!$B$19-COUNTIF(D22:K22,"Sim")-COUNTIF(D22:K22,"N/A")))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W22" s="24">
         <f>IF(A22="","",MAX(0,Config!$D$19-COUNTIF(L22:S22,"Sim")-COUNTIF(L22:S22,"N/A")))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="24">
         <f>IF(A22="","",V22+W22)</f>
@@ -4622,28 +4622,28 @@
       </c>
       <c r="Y22" s="29" t="str">
         <f>IF(OR(A22="",AA22=""),"",LEFT(AA22,LEN(AA22)-2))</f>
-        <v>Troco e maquininha conferidos; Orçamentos sem resposta revisados (lista da 15)</v>
+        <v>Troco e maquininha conferidos; Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
       </c>
       <c r="Z22" s="39">
         <f>IF(OR(A22="",X22=0),0,X22*100000+A22/100000)</f>
-        <v>200000.46227</v>
+        <v>200000.46198</v>
       </c>
       <c r="AA22" s="39" t="str">
         <f>IF(A22="","",IF(AND(Config!$B$10&lt;&gt;"",D22&lt;&gt;"Sim",D22&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E22&lt;&gt;"Sim",E22&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F22&lt;&gt;"Sim",F22&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G22&lt;&gt;"Sim",G22&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H22&lt;&gt;"Sim",H22&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I22&lt;&gt;"Sim",I22&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J22&lt;&gt;"Sim",J22&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K22&lt;&gt;"Sim",K22&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L22&lt;&gt;"Sim",L22&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M22&lt;&gt;"Sim",M22&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N22&lt;&gt;"Sim",N22&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O22&lt;&gt;"Sim",O22&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P22&lt;&gt;"Sim",P22&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q22&lt;&gt;"Sim",Q22&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R22&lt;&gt;"Sim",R22&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S22&lt;&gt;"Sim",S22&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v>Troco e maquininha conferidos; Orçamentos sem resposta revisados (lista da 15); </v>
+        <v>Troco e maquininha conferidos; Caixa do dia fechado e conferido (Pix, cartão, dinheiro); </v>
       </c>
       <c r="AB22" s="39">
         <f>IF(A22="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A22)+1)</f>
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="37" t="n">
-        <v>46230</v>
+        <v>46199</v>
       </c>
       <c r="B23" s="24" t="str">
         <f>IF(A23="","",CHOOSE(WEEKDAY(A23,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C23" s="38" t="inlineStr">
         <is>
@@ -4662,14 +4662,14 @@
       </c>
       <c r="F23" s="38" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G23" s="38" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="G23" s="38" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="H23" s="38" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I23" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J23" s="38" t="n"/>
@@ -4716,7 +4716,7 @@
       <c r="S23" s="38" t="n"/>
       <c r="T23" s="26">
         <f>IF(A23="","",IFERROR(COUNTIF(D23:K23,"Sim")/(Config!$B$19-COUNTIF(D23:K23,"N/A")),""))</f>
-        <v>0.8</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="U23" s="26">
         <f>IF(A23="","",IFERROR(COUNTIF(L23:S23,"Sim")/(Config!$D$19-COUNTIF(L23:S23,"N/A")),""))</f>
@@ -4736,28 +4736,28 @@
       </c>
       <c r="Y23" s="29" t="str">
         <f>IF(OR(A23="",AA23=""),"",LEFT(AA23,LEN(AA23)-2))</f>
-        <v>Salas e equipamentos prontos (ECG, MAPA, Holter)</v>
+        <v>Guias e autorizações de convênio do dia separadas</v>
       </c>
       <c r="Z23" s="39">
         <f>IF(OR(A23="",X23=0),0,X23*100000+A23/100000)</f>
-        <v>100000.4623</v>
+        <v>100000.46199</v>
       </c>
       <c r="AA23" s="39" t="str">
         <f>IF(A23="","",IF(AND(Config!$B$10&lt;&gt;"",D23&lt;&gt;"Sim",D23&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E23&lt;&gt;"Sim",E23&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F23&lt;&gt;"Sim",F23&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G23&lt;&gt;"Sim",G23&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H23&lt;&gt;"Sim",H23&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I23&lt;&gt;"Sim",I23&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J23&lt;&gt;"Sim",J23&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K23&lt;&gt;"Sim",K23&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L23&lt;&gt;"Sim",L23&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M23&lt;&gt;"Sim",M23&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N23&lt;&gt;"Sim",N23&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O23&lt;&gt;"Sim",O23&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P23&lt;&gt;"Sim",P23&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q23&lt;&gt;"Sim",Q23&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R23&lt;&gt;"Sim",R23&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S23&lt;&gt;"Sim",S23&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v>Salas e equipamentos prontos (ECG, MAPA, Holter); </v>
+        <v>Guias e autorizações de convênio do dia separadas; </v>
       </c>
       <c r="AB23" s="39">
         <f>IF(A23="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A23)+1)</f>
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="37" t="n">
-        <v>46231</v>
+        <v>46202</v>
       </c>
       <c r="B24" s="24" t="str">
         <f>IF(A24="","",CHOOSE(WEEKDAY(A24,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
       </c>
       <c r="AB24" s="39">
         <f>IF(A24="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A24)+1)</f>
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="37" t="n">
-        <v>46232</v>
+        <v>46203</v>
       </c>
       <c r="B25" s="24" t="str">
         <f>IF(A25="","",CHOOSE(WEEKDAY(A25,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C25" s="38" t="inlineStr">
         <is>
@@ -4976,16 +4976,16 @@
       </c>
       <c r="AB25" s="39">
         <f>IF(A25="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A25)+1)</f>
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="n">
-        <v>46233</v>
+        <v>46204</v>
       </c>
       <c r="B26" s="24" t="str">
         <f>IF(A26="","",CHOOSE(WEEKDAY(A26,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="Z26" s="39">
         <f>IF(OR(A26="",X26=0),0,X26*100000+A26/100000)</f>
-        <v>100000.46233</v>
+        <v>100000.46204</v>
       </c>
       <c r="AA26" s="39" t="str">
         <f>IF(A26="","",IF(AND(Config!$B$10&lt;&gt;"",D26&lt;&gt;"Sim",D26&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E26&lt;&gt;"Sim",E26&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F26&lt;&gt;"Sim",F26&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G26&lt;&gt;"Sim",G26&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H26&lt;&gt;"Sim",H26&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I26&lt;&gt;"Sim",I26&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J26&lt;&gt;"Sim",J26&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K26&lt;&gt;"Sim",K26&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L26&lt;&gt;"Sim",L26&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M26&lt;&gt;"Sim",M26&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N26&lt;&gt;"Sim",N26&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O26&lt;&gt;"Sim",O26&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P26&lt;&gt;"Sim",P26&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q26&lt;&gt;"Sim",Q26&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R26&lt;&gt;"Sim",R26&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S26&lt;&gt;"Sim",S26&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -5090,16 +5090,16 @@
       </c>
       <c r="AB26" s="39">
         <f>IF(A26="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A26)+1)</f>
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="n">
-        <v>46234</v>
+        <v>46205</v>
       </c>
       <c r="B27" s="24" t="str">
         <f>IF(A27="","",CHOOSE(WEEKDAY(A27,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I27" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J27" s="38" t="n"/>
@@ -5204,16 +5204,16 @@
       </c>
       <c r="AB27" s="39">
         <f>IF(A27="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A27)+1)</f>
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="n">
-        <v>46237</v>
+        <v>46206</v>
       </c>
       <c r="B28" s="24" t="str">
         <f>IF(A28="","",CHOOSE(WEEKDAY(A28,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="I28" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J28" s="38" t="n"/>
@@ -5318,16 +5318,16 @@
       </c>
       <c r="AB28" s="39">
         <f>IF(A28="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A28)+1)</f>
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="n">
-        <v>46238</v>
+        <v>46209</v>
       </c>
       <c r="B29" s="24" t="str">
         <f>IF(A29="","",CHOOSE(WEEKDAY(A29,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C29" s="38" t="inlineStr">
         <is>
@@ -5432,16 +5432,16 @@
       </c>
       <c r="AB29" s="39">
         <f>IF(A29="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A29)+1)</f>
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="n">
-        <v>46239</v>
+        <v>46210</v>
       </c>
       <c r="B30" s="24" t="str">
         <f>IF(A30="","",CHOOSE(WEEKDAY(A30,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z30" s="39">
         <f>IF(OR(A30="",X30=0),0,X30*100000+A30/100000)</f>
-        <v>200000.46239</v>
+        <v>200000.4621</v>
       </c>
       <c r="AA30" s="39" t="str">
         <f>IF(A30="","",IF(AND(Config!$B$10&lt;&gt;"",D30&lt;&gt;"Sim",D30&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E30&lt;&gt;"Sim",E30&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F30&lt;&gt;"Sim",F30&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G30&lt;&gt;"Sim",G30&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H30&lt;&gt;"Sim",H30&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I30&lt;&gt;"Sim",I30&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J30&lt;&gt;"Sim",J30&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K30&lt;&gt;"Sim",K30&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L30&lt;&gt;"Sim",L30&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M30&lt;&gt;"Sim",M30&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N30&lt;&gt;"Sim",N30&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O30&lt;&gt;"Sim",O30&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P30&lt;&gt;"Sim",P30&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q30&lt;&gt;"Sim",Q30&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R30&lt;&gt;"Sim",R30&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S30&lt;&gt;"Sim",S30&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -5546,16 +5546,16 @@
       </c>
       <c r="AB30" s="39">
         <f>IF(A30="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A30)+1)</f>
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="n">
-        <v>46240</v>
+        <v>46211</v>
       </c>
       <c r="B31" s="24" t="str">
         <f>IF(A31="","",CHOOSE(WEEKDAY(A31,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C31" s="38" t="inlineStr">
         <is>
@@ -5660,16 +5660,16 @@
       </c>
       <c r="AB31" s="39">
         <f>IF(A31="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A31)+1)</f>
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="n">
-        <v>46241</v>
+        <v>46212</v>
       </c>
       <c r="B32" s="24" t="str">
         <f>IF(A32="","",CHOOSE(WEEKDAY(A32,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="I32" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J32" s="38" t="n"/>
@@ -5774,16 +5774,16 @@
       </c>
       <c r="AB32" s="39">
         <f>IF(A32="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A32)+1)</f>
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="n">
-        <v>46244</v>
+        <v>46213</v>
       </c>
       <c r="B33" s="24" t="str">
         <f>IF(A33="","",CHOOSE(WEEKDAY(A33,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C33" s="38" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="I33" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J33" s="38" t="n"/>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="Z33" s="39">
         <f>IF(OR(A33="",X33=0),0,X33*100000+A33/100000)</f>
-        <v>100000.46244</v>
+        <v>100000.46213</v>
       </c>
       <c r="AA33" s="39" t="str">
         <f>IF(A33="","",IF(AND(Config!$B$10&lt;&gt;"",D33&lt;&gt;"Sim",D33&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E33&lt;&gt;"Sim",E33&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F33&lt;&gt;"Sim",F33&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G33&lt;&gt;"Sim",G33&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H33&lt;&gt;"Sim",H33&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I33&lt;&gt;"Sim",I33&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J33&lt;&gt;"Sim",J33&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K33&lt;&gt;"Sim",K33&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L33&lt;&gt;"Sim",L33&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M33&lt;&gt;"Sim",M33&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N33&lt;&gt;"Sim",N33&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O33&lt;&gt;"Sim",O33&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P33&lt;&gt;"Sim",P33&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q33&lt;&gt;"Sim",Q33&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R33&lt;&gt;"Sim",R33&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S33&lt;&gt;"Sim",S33&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -5888,16 +5888,16 @@
       </c>
       <c r="AB33" s="39">
         <f>IF(A33="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A33)+1)</f>
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="n">
-        <v>46245</v>
+        <v>46216</v>
       </c>
       <c r="B34" s="24" t="str">
         <f>IF(A34="","",CHOOSE(WEEKDAY(A34,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
@@ -6002,16 +6002,16 @@
       </c>
       <c r="AB34" s="39">
         <f>IF(A34="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A34)+1)</f>
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="n">
-        <v>46246</v>
+        <v>46217</v>
       </c>
       <c r="B35" s="24" t="str">
         <f>IF(A35="","",CHOOSE(WEEKDAY(A35,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C35" s="38" t="inlineStr">
         <is>
@@ -6116,16 +6116,16 @@
       </c>
       <c r="AB35" s="39">
         <f>IF(A35="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A35)+1)</f>
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="n">
-        <v>46247</v>
+        <v>46218</v>
       </c>
       <c r="B36" s="24" t="str">
         <f>IF(A36="","",CHOOSE(WEEKDAY(A36,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="Z36" s="39">
         <f>IF(OR(A36="",X36=0),0,X36*100000+A36/100000)</f>
-        <v>100000.46247</v>
+        <v>100000.46218</v>
       </c>
       <c r="AA36" s="39" t="str">
         <f>IF(A36="","",IF(AND(Config!$B$10&lt;&gt;"",D36&lt;&gt;"Sim",D36&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E36&lt;&gt;"Sim",E36&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F36&lt;&gt;"Sim",F36&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G36&lt;&gt;"Sim",G36&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H36&lt;&gt;"Sim",H36&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I36&lt;&gt;"Sim",I36&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J36&lt;&gt;"Sim",J36&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K36&lt;&gt;"Sim",K36&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L36&lt;&gt;"Sim",L36&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M36&lt;&gt;"Sim",M36&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N36&lt;&gt;"Sim",N36&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O36&lt;&gt;"Sim",O36&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P36&lt;&gt;"Sim",P36&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q36&lt;&gt;"Sim",Q36&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R36&lt;&gt;"Sim",R36&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S36&lt;&gt;"Sim",S36&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -6230,16 +6230,16 @@
       </c>
       <c r="AB36" s="39">
         <f>IF(A36="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A36)+1)</f>
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="37" t="n">
-        <v>46248</v>
+        <v>46219</v>
       </c>
       <c r="B37" s="24" t="str">
         <f>IF(A37="","",CHOOSE(WEEKDAY(A37,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C37" s="38" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="I37" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J37" s="38" t="n"/>
@@ -6344,16 +6344,16 @@
       </c>
       <c r="AB37" s="39">
         <f>IF(A37="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A37)+1)</f>
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="37" t="n">
-        <v>46251</v>
+        <v>46220</v>
       </c>
       <c r="B38" s="24" t="str">
         <f>IF(A38="","",CHOOSE(WEEKDAY(A38,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C38" s="38" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="I38" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J38" s="38" t="n"/>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Z38" s="39">
         <f>IF(OR(A38="",X38=0),0,X38*100000+A38/100000)</f>
-        <v>100000.46251</v>
+        <v>100000.4622</v>
       </c>
       <c r="AA38" s="39" t="str">
         <f>IF(A38="","",IF(AND(Config!$B$10&lt;&gt;"",D38&lt;&gt;"Sim",D38&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E38&lt;&gt;"Sim",E38&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F38&lt;&gt;"Sim",F38&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G38&lt;&gt;"Sim",G38&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H38&lt;&gt;"Sim",H38&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I38&lt;&gt;"Sim",I38&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J38&lt;&gt;"Sim",J38&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K38&lt;&gt;"Sim",K38&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L38&lt;&gt;"Sim",L38&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M38&lt;&gt;"Sim",M38&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N38&lt;&gt;"Sim",N38&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O38&lt;&gt;"Sim",O38&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P38&lt;&gt;"Sim",P38&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q38&lt;&gt;"Sim",Q38&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R38&lt;&gt;"Sim",R38&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S38&lt;&gt;"Sim",S38&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -6458,16 +6458,16 @@
       </c>
       <c r="AB38" s="39">
         <f>IF(A38="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A38)+1)</f>
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="37" t="n">
-        <v>46252</v>
+        <v>46223</v>
       </c>
       <c r="B39" s="24" t="str">
         <f>IF(A39="","",CHOOSE(WEEKDAY(A39,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C39" s="38" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z39" s="39">
         <f>IF(OR(A39="",X39=0),0,X39*100000+A39/100000)</f>
-        <v>200000.46252</v>
+        <v>200000.46223</v>
       </c>
       <c r="AA39" s="39" t="str">
         <f>IF(A39="","",IF(AND(Config!$B$10&lt;&gt;"",D39&lt;&gt;"Sim",D39&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E39&lt;&gt;"Sim",E39&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F39&lt;&gt;"Sim",F39&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G39&lt;&gt;"Sim",G39&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H39&lt;&gt;"Sim",H39&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I39&lt;&gt;"Sim",I39&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J39&lt;&gt;"Sim",J39&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K39&lt;&gt;"Sim",K39&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L39&lt;&gt;"Sim",L39&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M39&lt;&gt;"Sim",M39&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N39&lt;&gt;"Sim",N39&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O39&lt;&gt;"Sim",O39&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P39&lt;&gt;"Sim",P39&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q39&lt;&gt;"Sim",Q39&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R39&lt;&gt;"Sim",R39&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S39&lt;&gt;"Sim",S39&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -6572,16 +6572,16 @@
       </c>
       <c r="AB39" s="39">
         <f>IF(A39="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A39)+1)</f>
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="37" t="n">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="B40" s="24" t="str">
         <f>IF(A40="","",CHOOSE(WEEKDAY(A40,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C40" s="38" t="inlineStr">
         <is>
@@ -6686,16 +6686,16 @@
       </c>
       <c r="AB40" s="39">
         <f>IF(A40="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A40)+1)</f>
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="37" t="n">
-        <v>46254</v>
+        <v>46225</v>
       </c>
       <c r="B41" s="24" t="str">
         <f>IF(A41="","",CHOOSE(WEEKDAY(A41,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
@@ -6800,16 +6800,16 @@
       </c>
       <c r="AB41" s="39">
         <f>IF(A41="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A41)+1)</f>
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="37" t="n">
-        <v>46255</v>
+        <v>46226</v>
       </c>
       <c r="B42" s="24" t="str">
         <f>IF(A42="","",CHOOSE(WEEKDAY(A42,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C42" s="38" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="I42" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J42" s="38" t="n"/>
@@ -6882,7 +6882,7 @@
       <c r="S42" s="38" t="n"/>
       <c r="T42" s="26">
         <f>IF(A42="","",IFERROR(COUNTIF(D42:K42,"Sim")/(Config!$B$19-COUNTIF(D42:K42,"N/A")),""))</f>
-        <v>0.833333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="U42" s="26">
         <f>IF(A42="","",IFERROR(COUNTIF(L42:S42,"Sim")/(Config!$D$19-COUNTIF(L42:S42,"N/A")),""))</f>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="Z42" s="39">
         <f>IF(OR(A42="",X42=0),0,X42*100000+A42/100000)</f>
-        <v>100000.46255</v>
+        <v>100000.46226</v>
       </c>
       <c r="AA42" s="39" t="str">
         <f>IF(A42="","",IF(AND(Config!$B$10&lt;&gt;"",D42&lt;&gt;"Sim",D42&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E42&lt;&gt;"Sim",E42&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F42&lt;&gt;"Sim",F42&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G42&lt;&gt;"Sim",G42&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H42&lt;&gt;"Sim",H42&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I42&lt;&gt;"Sim",I42&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J42&lt;&gt;"Sim",J42&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K42&lt;&gt;"Sim",K42&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L42&lt;&gt;"Sim",L42&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M42&lt;&gt;"Sim",M42&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N42&lt;&gt;"Sim",N42&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O42&lt;&gt;"Sim",O42&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P42&lt;&gt;"Sim",P42&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q42&lt;&gt;"Sim",Q42&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R42&lt;&gt;"Sim",R42&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S42&lt;&gt;"Sim",S42&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -6914,16 +6914,16 @@
       </c>
       <c r="AB42" s="39">
         <f>IF(A42="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A42)+1)</f>
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="37" t="n">
-        <v>46258</v>
+        <v>46227</v>
       </c>
       <c r="B43" s="24" t="str">
         <f>IF(A43="","",CHOOSE(WEEKDAY(A43,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C43" s="38" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="I43" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J43" s="38" t="n"/>
@@ -7028,16 +7028,16 @@
       </c>
       <c r="AB43" s="39">
         <f>IF(A43="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A43)+1)</f>
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="37" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="B44" s="24" t="str">
         <f>IF(A44="","",CHOOSE(WEEKDAY(A44,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C44" s="38" t="inlineStr">
         <is>
@@ -7142,16 +7142,16 @@
       </c>
       <c r="AB44" s="39">
         <f>IF(A44="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A44)+1)</f>
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="37" t="n">
-        <v>46260</v>
+        <v>46231</v>
       </c>
       <c r="B45" s="24" t="str">
         <f>IF(A45="","",CHOOSE(WEEKDAY(A45,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C45" s="38" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z45" s="39">
         <f>IF(OR(A45="",X45=0),0,X45*100000+A45/100000)</f>
-        <v>300000.4626</v>
+        <v>300000.46231</v>
       </c>
       <c r="AA45" s="39" t="str">
         <f>IF(A45="","",IF(AND(Config!$B$10&lt;&gt;"",D45&lt;&gt;"Sim",D45&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E45&lt;&gt;"Sim",E45&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F45&lt;&gt;"Sim",F45&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G45&lt;&gt;"Sim",G45&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H45&lt;&gt;"Sim",H45&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I45&lt;&gt;"Sim",I45&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J45&lt;&gt;"Sim",J45&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K45&lt;&gt;"Sim",K45&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L45&lt;&gt;"Sim",L45&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M45&lt;&gt;"Sim",M45&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N45&lt;&gt;"Sim",N45&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O45&lt;&gt;"Sim",O45&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P45&lt;&gt;"Sim",P45&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q45&lt;&gt;"Sim",Q45&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R45&lt;&gt;"Sim",R45&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S45&lt;&gt;"Sim",S45&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -7256,16 +7256,16 @@
       </c>
       <c r="AB45" s="39">
         <f>IF(A45="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A45)+1)</f>
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="37" t="n">
-        <v>46261</v>
+        <v>46232</v>
       </c>
       <c r="B46" s="24" t="str">
         <f>IF(A46="","",CHOOSE(WEEKDAY(A46,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C46" s="38" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="Z46" s="39">
         <f>IF(OR(A46="",X46=0),0,X46*100000+A46/100000)</f>
-        <v>100000.46261</v>
+        <v>100000.46232</v>
       </c>
       <c r="AA46" s="39" t="str">
         <f>IF(A46="","",IF(AND(Config!$B$10&lt;&gt;"",D46&lt;&gt;"Sim",D46&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E46&lt;&gt;"Sim",E46&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F46&lt;&gt;"Sim",F46&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G46&lt;&gt;"Sim",G46&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H46&lt;&gt;"Sim",H46&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I46&lt;&gt;"Sim",I46&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J46&lt;&gt;"Sim",J46&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K46&lt;&gt;"Sim",K46&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L46&lt;&gt;"Sim",L46&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M46&lt;&gt;"Sim",M46&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N46&lt;&gt;"Sim",N46&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O46&lt;&gt;"Sim",O46&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P46&lt;&gt;"Sim",P46&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q46&lt;&gt;"Sim",Q46&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R46&lt;&gt;"Sim",R46&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S46&lt;&gt;"Sim",S46&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -7370,16 +7370,16 @@
       </c>
       <c r="AB46" s="39">
         <f>IF(A46="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A46)+1)</f>
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="37" t="n">
-        <v>46262</v>
+        <v>46233</v>
       </c>
       <c r="B47" s="24" t="str">
         <f>IF(A47="","",CHOOSE(WEEKDAY(A47,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C47" s="38" t="inlineStr">
         <is>
@@ -7413,19 +7413,19 @@
       </c>
       <c r="I47" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J47" s="38" t="n"/>
       <c r="K47" s="38" t="n"/>
       <c r="L47" s="38" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M47" s="38" t="inlineStr">
+        <is>
           <t>Não</t>
-        </is>
-      </c>
-      <c r="M47" s="38" t="inlineStr">
-        <is>
-          <t>Sim</t>
         </is>
       </c>
       <c r="N47" s="38" t="inlineStr">
@@ -7472,28 +7472,28 @@
       </c>
       <c r="Y47" s="29" t="str">
         <f>IF(OR(A47="",AA47=""),"",LEFT(AA47,LEN(AA47)-2))</f>
-        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
+        <v>Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="Z47" s="39">
         <f>IF(OR(A47="",X47=0),0,X47*100000+A47/100000)</f>
-        <v>100000.46262</v>
+        <v>100000.46233</v>
       </c>
       <c r="AA47" s="39" t="str">
         <f>IF(A47="","",IF(AND(Config!$B$10&lt;&gt;"",D47&lt;&gt;"Sim",D47&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E47&lt;&gt;"Sim",E47&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F47&lt;&gt;"Sim",F47&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G47&lt;&gt;"Sim",G47&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H47&lt;&gt;"Sim",H47&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I47&lt;&gt;"Sim",I47&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J47&lt;&gt;"Sim",J47&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K47&lt;&gt;"Sim",K47&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L47&lt;&gt;"Sim",L47&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M47&lt;&gt;"Sim",M47&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N47&lt;&gt;"Sim",N47&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O47&lt;&gt;"Sim",O47&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P47&lt;&gt;"Sim",P47&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q47&lt;&gt;"Sim",Q47&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R47&lt;&gt;"Sim",R47&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S47&lt;&gt;"Sim",S47&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); </v>
+        <v>Fechamento do dia lançado no Caixa (09); </v>
       </c>
       <c r="AB47" s="39">
         <f>IF(A47="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A47)+1)</f>
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="37" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B48" s="24" t="str">
         <f>IF(A48="","",CHOOSE(WEEKDAY(A48,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Segunda</v>
+        <v>Sexta</v>
       </c>
       <c r="C48" s="38" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="I48" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J48" s="38" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z48" s="39">
         <f>IF(OR(A48="",X48=0),0,X48*100000+A48/100000)</f>
-        <v>100000.46265</v>
+        <v>100000.46234</v>
       </c>
       <c r="AA48" s="39" t="str">
         <f>IF(A48="","",IF(AND(Config!$B$10&lt;&gt;"",D48&lt;&gt;"Sim",D48&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E48&lt;&gt;"Sim",E48&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F48&lt;&gt;"Sim",F48&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G48&lt;&gt;"Sim",G48&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H48&lt;&gt;"Sim",H48&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I48&lt;&gt;"Sim",I48&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J48&lt;&gt;"Sim",J48&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K48&lt;&gt;"Sim",K48&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L48&lt;&gt;"Sim",L48&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M48&lt;&gt;"Sim",M48&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N48&lt;&gt;"Sim",N48&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O48&lt;&gt;"Sim",O48&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P48&lt;&gt;"Sim",P48&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q48&lt;&gt;"Sim",Q48&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R48&lt;&gt;"Sim",R48&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S48&lt;&gt;"Sim",S48&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -7598,16 +7598,16 @@
       </c>
       <c r="AB48" s="39">
         <f>IF(A48="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A48)+1)</f>
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="37" t="n">
-        <v>46266</v>
+        <v>46237</v>
       </c>
       <c r="B49" s="24" t="str">
         <f>IF(A49="","",CHOOSE(WEEKDAY(A49,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Segunda</v>
       </c>
       <c r="C49" s="38" t="inlineStr">
         <is>
@@ -7712,16 +7712,16 @@
       </c>
       <c r="AB49" s="39">
         <f>IF(A49="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A49)+1)</f>
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="37" t="n">
-        <v>46267</v>
+        <v>46238</v>
       </c>
       <c r="B50" s="24" t="str">
         <f>IF(A50="","",CHOOSE(WEEKDAY(A50,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Terça</v>
       </c>
       <c r="C50" s="38" t="inlineStr">
         <is>
@@ -7826,16 +7826,16 @@
       </c>
       <c r="AB50" s="39">
         <f>IF(A50="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A50)+1)</f>
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="37" t="n">
-        <v>46268</v>
+        <v>46239</v>
       </c>
       <c r="B51" s="24" t="str">
         <f>IF(A51="","",CHOOSE(WEEKDAY(A51,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Quarta</v>
       </c>
       <c r="C51" s="38" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="Z51" s="39">
         <f>IF(OR(A51="",X51=0),0,X51*100000+A51/100000)</f>
-        <v>200000.46268</v>
+        <v>200000.46239</v>
       </c>
       <c r="AA51" s="39" t="str">
         <f>IF(A51="","",IF(AND(Config!$B$10&lt;&gt;"",D51&lt;&gt;"Sim",D51&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E51&lt;&gt;"Sim",E51&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F51&lt;&gt;"Sim",F51&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G51&lt;&gt;"Sim",G51&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H51&lt;&gt;"Sim",H51&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I51&lt;&gt;"Sim",I51&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J51&lt;&gt;"Sim",J51&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K51&lt;&gt;"Sim",K51&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L51&lt;&gt;"Sim",L51&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M51&lt;&gt;"Sim",M51&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N51&lt;&gt;"Sim",N51&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O51&lt;&gt;"Sim",O51&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P51&lt;&gt;"Sim",P51&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q51&lt;&gt;"Sim",Q51&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R51&lt;&gt;"Sim",R51&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S51&lt;&gt;"Sim",S51&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -7940,16 +7940,16 @@
       </c>
       <c r="AB51" s="39">
         <f>IF(A51="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A51)+1)</f>
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="37" t="n">
-        <v>46269</v>
+        <v>46240</v>
       </c>
       <c r="B52" s="24" t="str">
         <f>IF(A52="","",CHOOSE(WEEKDAY(A52,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quinta</v>
       </c>
       <c r="C52" s="38" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="I52" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J52" s="38" t="n"/>
@@ -8054,16 +8054,16 @@
       </c>
       <c r="AB52" s="39">
         <f>IF(A52="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A52)+1)</f>
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="37" t="n">
-        <v>46273</v>
+        <v>46241</v>
       </c>
       <c r="B53" s="24" t="str">
         <f>IF(A53="","",CHOOSE(WEEKDAY(A53,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Terça</v>
+        <v>Sexta</v>
       </c>
       <c r="C53" s="38" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="I53" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="J53" s="38" t="n"/>
@@ -8168,16 +8168,16 @@
       </c>
       <c r="AB53" s="39">
         <f>IF(A53="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A53)+1)</f>
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="37" t="n">
-        <v>46274</v>
+        <v>46244</v>
       </c>
       <c r="B54" s="24" t="str">
         <f>IF(A54="","",CHOOSE(WEEKDAY(A54,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quarta</v>
+        <v>Segunda</v>
       </c>
       <c r="C54" s="38" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z54" s="39">
         <f>IF(OR(A54="",X54=0),0,X54*100000+A54/100000)</f>
-        <v>100000.46274</v>
+        <v>100000.46244</v>
       </c>
       <c r="AA54" s="39" t="str">
         <f>IF(A54="","",IF(AND(Config!$B$10&lt;&gt;"",D54&lt;&gt;"Sim",D54&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E54&lt;&gt;"Sim",E54&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F54&lt;&gt;"Sim",F54&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G54&lt;&gt;"Sim",G54&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H54&lt;&gt;"Sim",H54&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I54&lt;&gt;"Sim",I54&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J54&lt;&gt;"Sim",J54&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K54&lt;&gt;"Sim",K54&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L54&lt;&gt;"Sim",L54&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M54&lt;&gt;"Sim",M54&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N54&lt;&gt;"Sim",N54&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O54&lt;&gt;"Sim",O54&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P54&lt;&gt;"Sim",P54&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q54&lt;&gt;"Sim",Q54&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R54&lt;&gt;"Sim",R54&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S54&lt;&gt;"Sim",S54&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
@@ -8282,16 +8282,16 @@
       </c>
       <c r="AB54" s="39">
         <f>IF(A54="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A54)+1)</f>
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="37" t="n">
-        <v>46275</v>
+        <v>46245</v>
       </c>
       <c r="B55" s="24" t="str">
         <f>IF(A55="","",CHOOSE(WEEKDAY(A55,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Quinta</v>
+        <v>Terça</v>
       </c>
       <c r="C55" s="38" t="inlineStr">
         <is>
@@ -8335,10 +8335,14 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="M55" s="38" t="n"/>
+      <c r="M55" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="N55" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O55" s="38" t="inlineStr">
@@ -8380,28 +8384,28 @@
       </c>
       <c r="Y55" s="29" t="str">
         <f>IF(OR(A55="",AA55=""),"",LEFT(AA55,LEN(AA55)-2))</f>
-        <v>Fechamento do dia lançado no Caixa (09)</v>
+        <v>Situação de cada horário marcada (realizado, falta, cancelado)</v>
       </c>
       <c r="Z55" s="39">
         <f>IF(OR(A55="",X55=0),0,X55*100000+A55/100000)</f>
-        <v>100000.46275</v>
+        <v>100000.46245</v>
       </c>
       <c r="AA55" s="39" t="str">
         <f>IF(A55="","",IF(AND(Config!$B$10&lt;&gt;"",D55&lt;&gt;"Sim",D55&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E55&lt;&gt;"Sim",E55&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F55&lt;&gt;"Sim",F55&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G55&lt;&gt;"Sim",G55&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H55&lt;&gt;"Sim",H55&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I55&lt;&gt;"Sim",I55&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J55&lt;&gt;"Sim",J55&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K55&lt;&gt;"Sim",K55&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L55&lt;&gt;"Sim",L55&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M55&lt;&gt;"Sim",M55&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N55&lt;&gt;"Sim",N55&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O55&lt;&gt;"Sim",O55&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P55&lt;&gt;"Sim",P55&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q55&lt;&gt;"Sim",Q55&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R55&lt;&gt;"Sim",R55&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S55&lt;&gt;"Sim",S55&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v>Fechamento do dia lançado no Caixa (09); </v>
+        <v>Situação de cada horário marcada (realizado, falta, cancelado); </v>
       </c>
       <c r="AB55" s="39">
         <f>IF(A55="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A55)+1)</f>
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="37" t="n">
-        <v>46276</v>
+        <v>46246</v>
       </c>
       <c r="B56" s="24" t="str">
         <f>IF(A56="","",CHOOSE(WEEKDAY(A56,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v>Sexta</v>
+        <v>Quarta</v>
       </c>
       <c r="C56" s="38" t="inlineStr">
         <is>
@@ -8435,7 +8439,7 @@
       </c>
       <c r="I56" s="38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J56" s="38" t="n"/>
@@ -8445,7 +8449,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="M56" s="38" t="n"/>
+      <c r="M56" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="N56" s="38" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -8453,7 +8461,7 @@
       </c>
       <c r="O56" s="38" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P56" s="38" t="inlineStr">
@@ -8474,7 +8482,7 @@
       </c>
       <c r="U56" s="26">
         <f>IF(A56="","",IFERROR(COUNTIF(L56:S56,"Sim")/(Config!$D$19-COUNTIF(L56:S56,"N/A")),""))</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="V56" s="24">
         <f>IF(A56="","",MAX(0,Config!$B$19-COUNTIF(D56:K56,"Sim")-COUNTIF(D56:K56,"N/A")))</f>
@@ -8482,191 +8490,353 @@
       </c>
       <c r="W56" s="24">
         <f>IF(A56="","",MAX(0,Config!$D$19-COUNTIF(L56:S56,"Sim")-COUNTIF(L56:S56,"N/A")))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X56" s="24">
         <f>IF(A56="","",V56+W56)</f>
-        <v>2</v>
-      </c>
-      <c r="Y56" s="29" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="29">
         <f>IF(OR(A56="",AA56=""),"",LEFT(AA56,LEN(AA56)-2))</f>
-        <v>Fechamento do dia lançado no Caixa (09); Guias do dia conferidas e guardadas para o lote (13)</v>
+        <v/>
       </c>
       <c r="Z56" s="39">
         <f>IF(OR(A56="",X56=0),0,X56*100000+A56/100000)</f>
-        <v>200000.46276</v>
-      </c>
-      <c r="AA56" s="39" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="39">
         <f>IF(A56="","",IF(AND(Config!$B$10&lt;&gt;"",D56&lt;&gt;"Sim",D56&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E56&lt;&gt;"Sim",E56&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F56&lt;&gt;"Sim",F56&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G56&lt;&gt;"Sim",G56&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H56&lt;&gt;"Sim",H56&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I56&lt;&gt;"Sim",I56&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J56&lt;&gt;"Sim",J56&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K56&lt;&gt;"Sim",K56&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L56&lt;&gt;"Sim",L56&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M56&lt;&gt;"Sim",M56&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N56&lt;&gt;"Sim",N56&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O56&lt;&gt;"Sim",O56&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P56&lt;&gt;"Sim",P56&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q56&lt;&gt;"Sim",Q56&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R56&lt;&gt;"Sim",R56&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S56&lt;&gt;"Sim",S56&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v>Fechamento do dia lançado no Caixa (09); Guias do dia conferidas e guardadas para o lote (13); </v>
+        <v/>
       </c>
       <c r="AB56" s="39">
         <f>IF(A56="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A56)+1)</f>
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="37" t="n"/>
-      <c r="B57" s="24">
+      <c r="A57" s="37" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B57" s="24" t="str">
         <f>IF(A57="","",CHOOSE(WEEKDAY(A57,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C57" s="38" t="n"/>
-      <c r="D57" s="38" t="n"/>
-      <c r="E57" s="38" t="n"/>
-      <c r="F57" s="38" t="n"/>
-      <c r="G57" s="38" t="n"/>
-      <c r="H57" s="38" t="n"/>
-      <c r="I57" s="38" t="n"/>
+        <v>Quinta</v>
+      </c>
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E57" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J57" s="38" t="n"/>
       <c r="K57" s="38" t="n"/>
-      <c r="L57" s="38" t="n"/>
-      <c r="M57" s="38" t="n"/>
-      <c r="N57" s="38" t="n"/>
-      <c r="O57" s="38" t="n"/>
-      <c r="P57" s="38" t="n"/>
-      <c r="Q57" s="38" t="n"/>
+      <c r="L57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q57" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R57" s="38" t="n"/>
       <c r="S57" s="38" t="n"/>
       <c r="T57" s="26">
         <f>IF(A57="","",IFERROR(COUNTIF(D57:K57,"Sim")/(Config!$B$19-COUNTIF(D57:K57,"N/A")),""))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="U57" s="26">
         <f>IF(A57="","",IFERROR(COUNTIF(L57:S57,"Sim")/(Config!$D$19-COUNTIF(L57:S57,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V57" s="24">
         <f>IF(A57="","",MAX(0,Config!$B$19-COUNTIF(D57:K57,"Sim")-COUNTIF(D57:K57,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W57" s="24">
         <f>IF(A57="","",MAX(0,Config!$D$19-COUNTIF(L57:S57,"Sim")-COUNTIF(L57:S57,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X57" s="24">
         <f>IF(A57="","",V57+W57)</f>
-        <v/>
-      </c>
-      <c r="Y57" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="29" t="str">
         <f>IF(OR(A57="",AA57=""),"",LEFT(AA57,LEN(AA57)-2))</f>
-        <v/>
+        <v>Faltas e cancelamentos de ontem registrados na agenda</v>
       </c>
       <c r="Z57" s="39">
         <f>IF(OR(A57="",X57=0),0,X57*100000+A57/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA57" s="39">
+        <v>100000.46247</v>
+      </c>
+      <c r="AA57" s="39" t="str">
         <f>IF(A57="","",IF(AND(Config!$B$10&lt;&gt;"",D57&lt;&gt;"Sim",D57&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E57&lt;&gt;"Sim",E57&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F57&lt;&gt;"Sim",F57&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G57&lt;&gt;"Sim",G57&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H57&lt;&gt;"Sim",H57&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I57&lt;&gt;"Sim",I57&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J57&lt;&gt;"Sim",J57&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K57&lt;&gt;"Sim",K57&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L57&lt;&gt;"Sim",L57&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M57&lt;&gt;"Sim",M57&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N57&lt;&gt;"Sim",N57&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O57&lt;&gt;"Sim",O57&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P57&lt;&gt;"Sim",P57&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q57&lt;&gt;"Sim",Q57&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R57&lt;&gt;"Sim",R57&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S57&lt;&gt;"Sim",S57&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; </v>
       </c>
       <c r="AB57" s="39">
         <f>IF(A57="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A57)+1)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="37" t="n"/>
-      <c r="B58" s="24">
+      <c r="A58" s="37" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B58" s="24" t="str">
         <f>IF(A58="","",CHOOSE(WEEKDAY(A58,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="38" t="n"/>
-      <c r="H58" s="38" t="n"/>
-      <c r="I58" s="38" t="n"/>
+        <v>Sexta</v>
+      </c>
+      <c r="C58" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="J58" s="38" t="n"/>
       <c r="K58" s="38" t="n"/>
-      <c r="L58" s="38" t="n"/>
-      <c r="M58" s="38" t="n"/>
-      <c r="N58" s="38" t="n"/>
-      <c r="O58" s="38" t="n"/>
-      <c r="P58" s="38" t="n"/>
-      <c r="Q58" s="38" t="n"/>
+      <c r="L58" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q58" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R58" s="38" t="n"/>
       <c r="S58" s="38" t="n"/>
       <c r="T58" s="26">
         <f>IF(A58="","",IFERROR(COUNTIF(D58:K58,"Sim")/(Config!$B$19-COUNTIF(D58:K58,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U58" s="26">
         <f>IF(A58="","",IFERROR(COUNTIF(L58:S58,"Sim")/(Config!$D$19-COUNTIF(L58:S58,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V58" s="24">
         <f>IF(A58="","",MAX(0,Config!$B$19-COUNTIF(D58:K58,"Sim")-COUNTIF(D58:K58,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W58" s="24">
         <f>IF(A58="","",MAX(0,Config!$D$19-COUNTIF(L58:S58,"Sim")-COUNTIF(L58:S58,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X58" s="24">
         <f>IF(A58="","",V58+W58)</f>
-        <v/>
-      </c>
-      <c r="Y58" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="29" t="str">
         <f>IF(OR(A58="",AA58=""),"",LEFT(AA58,LEN(AA58)-2))</f>
-        <v/>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro)</v>
       </c>
       <c r="Z58" s="39">
         <f>IF(OR(A58="",X58=0),0,X58*100000+A58/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA58" s="39">
+        <v>100000.46248</v>
+      </c>
+      <c r="AA58" s="39" t="str">
         <f>IF(A58="","",IF(AND(Config!$B$10&lt;&gt;"",D58&lt;&gt;"Sim",D58&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E58&lt;&gt;"Sim",E58&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F58&lt;&gt;"Sim",F58&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G58&lt;&gt;"Sim",G58&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H58&lt;&gt;"Sim",H58&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I58&lt;&gt;"Sim",I58&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J58&lt;&gt;"Sim",J58&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K58&lt;&gt;"Sim",K58&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L58&lt;&gt;"Sim",L58&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M58&lt;&gt;"Sim",M58&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N58&lt;&gt;"Sim",N58&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O58&lt;&gt;"Sim",O58&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P58&lt;&gt;"Sim",P58&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q58&lt;&gt;"Sim",Q58&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R58&lt;&gt;"Sim",R58&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S58&lt;&gt;"Sim",S58&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); </v>
       </c>
       <c r="AB58" s="39">
         <f>IF(A58="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A58)+1)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="37" t="n"/>
-      <c r="B59" s="24">
+      <c r="A59" s="37" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B59" s="24" t="str">
         <f>IF(A59="","",CHOOSE(WEEKDAY(A59,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C59" s="38" t="n"/>
-      <c r="D59" s="38" t="n"/>
-      <c r="E59" s="38" t="n"/>
-      <c r="F59" s="38" t="n"/>
-      <c r="G59" s="38" t="n"/>
-      <c r="H59" s="38" t="n"/>
-      <c r="I59" s="38" t="n"/>
+        <v>Segunda</v>
+      </c>
+      <c r="C59" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J59" s="38" t="n"/>
       <c r="K59" s="38" t="n"/>
-      <c r="L59" s="38" t="n"/>
-      <c r="M59" s="38" t="n"/>
-      <c r="N59" s="38" t="n"/>
-      <c r="O59" s="38" t="n"/>
-      <c r="P59" s="38" t="n"/>
-      <c r="Q59" s="38" t="n"/>
+      <c r="L59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q59" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R59" s="38" t="n"/>
       <c r="S59" s="38" t="n"/>
       <c r="T59" s="26">
         <f>IF(A59="","",IFERROR(COUNTIF(D59:K59,"Sim")/(Config!$B$19-COUNTIF(D59:K59,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U59" s="26">
         <f>IF(A59="","",IFERROR(COUNTIF(L59:S59,"Sim")/(Config!$D$19-COUNTIF(L59:S59,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V59" s="24">
         <f>IF(A59="","",MAX(0,Config!$B$19-COUNTIF(D59:K59,"Sim")-COUNTIF(D59:K59,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W59" s="24">
         <f>IF(A59="","",MAX(0,Config!$D$19-COUNTIF(L59:S59,"Sim")-COUNTIF(L59:S59,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X59" s="24">
         <f>IF(A59="","",V59+W59)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y59" s="29">
         <f>IF(OR(A59="",AA59=""),"",LEFT(AA59,LEN(AA59)-2))</f>
@@ -8682,51 +8852,105 @@
       </c>
       <c r="AB59" s="39">
         <f>IF(A59="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A59)+1)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="37" t="n"/>
-      <c r="B60" s="24">
+      <c r="A60" s="37" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B60" s="24" t="str">
         <f>IF(A60="","",CHOOSE(WEEKDAY(A60,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="38" t="n"/>
-      <c r="E60" s="38" t="n"/>
-      <c r="F60" s="38" t="n"/>
-      <c r="G60" s="38" t="n"/>
-      <c r="H60" s="38" t="n"/>
-      <c r="I60" s="38" t="n"/>
+        <v>Terça</v>
+      </c>
+      <c r="C60" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J60" s="38" t="n"/>
       <c r="K60" s="38" t="n"/>
-      <c r="L60" s="38" t="n"/>
-      <c r="M60" s="38" t="n"/>
-      <c r="N60" s="38" t="n"/>
-      <c r="O60" s="38" t="n"/>
-      <c r="P60" s="38" t="n"/>
-      <c r="Q60" s="38" t="n"/>
+      <c r="L60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q60" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R60" s="38" t="n"/>
       <c r="S60" s="38" t="n"/>
       <c r="T60" s="26">
         <f>IF(A60="","",IFERROR(COUNTIF(D60:K60,"Sim")/(Config!$B$19-COUNTIF(D60:K60,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U60" s="26">
         <f>IF(A60="","",IFERROR(COUNTIF(L60:S60,"Sim")/(Config!$D$19-COUNTIF(L60:S60,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V60" s="24">
         <f>IF(A60="","",MAX(0,Config!$B$19-COUNTIF(D60:K60,"Sim")-COUNTIF(D60:K60,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W60" s="24">
         <f>IF(A60="","",MAX(0,Config!$D$19-COUNTIF(L60:S60,"Sim")-COUNTIF(L60:S60,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X60" s="24">
         <f>IF(A60="","",V60+W60)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y60" s="29">
         <f>IF(OR(A60="",AA60=""),"",LEFT(AA60,LEN(AA60)-2))</f>
@@ -8742,111 +8966,219 @@
       </c>
       <c r="AB60" s="39">
         <f>IF(A60="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A60)+1)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="n"/>
-      <c r="B61" s="24">
+      <c r="A61" s="37" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B61" s="24" t="str">
         <f>IF(A61="","",CHOOSE(WEEKDAY(A61,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C61" s="38" t="n"/>
-      <c r="D61" s="38" t="n"/>
-      <c r="E61" s="38" t="n"/>
-      <c r="F61" s="38" t="n"/>
-      <c r="G61" s="38" t="n"/>
-      <c r="H61" s="38" t="n"/>
-      <c r="I61" s="38" t="n"/>
+        <v>Quarta</v>
+      </c>
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J61" s="38" t="n"/>
       <c r="K61" s="38" t="n"/>
-      <c r="L61" s="38" t="n"/>
-      <c r="M61" s="38" t="n"/>
-      <c r="N61" s="38" t="n"/>
-      <c r="O61" s="38" t="n"/>
-      <c r="P61" s="38" t="n"/>
-      <c r="Q61" s="38" t="n"/>
+      <c r="L61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M61" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="N61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q61" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R61" s="38" t="n"/>
       <c r="S61" s="38" t="n"/>
       <c r="T61" s="26">
         <f>IF(A61="","",IFERROR(COUNTIF(D61:K61,"Sim")/(Config!$B$19-COUNTIF(D61:K61,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U61" s="26">
         <f>IF(A61="","",IFERROR(COUNTIF(L61:S61,"Sim")/(Config!$D$19-COUNTIF(L61:S61,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V61" s="24">
         <f>IF(A61="","",MAX(0,Config!$B$19-COUNTIF(D61:K61,"Sim")-COUNTIF(D61:K61,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W61" s="24">
         <f>IF(A61="","",MAX(0,Config!$D$19-COUNTIF(L61:S61,"Sim")-COUNTIF(L61:S61,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X61" s="24">
         <f>IF(A61="","",V61+W61)</f>
-        <v/>
-      </c>
-      <c r="Y61" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="29" t="str">
         <f>IF(OR(A61="",AA61=""),"",LEFT(AA61,LEN(AA61)-2))</f>
-        <v/>
+        <v>Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="Z61" s="39">
         <f>IF(OR(A61="",X61=0),0,X61*100000+A61/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA61" s="39">
+        <v>100000.46253</v>
+      </c>
+      <c r="AA61" s="39" t="str">
         <f>IF(A61="","",IF(AND(Config!$B$10&lt;&gt;"",D61&lt;&gt;"Sim",D61&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E61&lt;&gt;"Sim",E61&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F61&lt;&gt;"Sim",F61&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G61&lt;&gt;"Sim",G61&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H61&lt;&gt;"Sim",H61&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I61&lt;&gt;"Sim",I61&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J61&lt;&gt;"Sim",J61&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K61&lt;&gt;"Sim",K61&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L61&lt;&gt;"Sim",L61&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M61&lt;&gt;"Sim",M61&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N61&lt;&gt;"Sim",N61&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O61&lt;&gt;"Sim",O61&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P61&lt;&gt;"Sim",P61&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q61&lt;&gt;"Sim",Q61&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R61&lt;&gt;"Sim",R61&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S61&lt;&gt;"Sim",S61&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Fechamento do dia lançado no Caixa (09); </v>
       </c>
       <c r="AB61" s="39">
         <f>IF(A61="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A61)+1)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="37" t="n"/>
-      <c r="B62" s="24">
+      <c r="A62" s="37" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B62" s="24" t="str">
         <f>IF(A62="","",CHOOSE(WEEKDAY(A62,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C62" s="38" t="n"/>
-      <c r="D62" s="38" t="n"/>
-      <c r="E62" s="38" t="n"/>
-      <c r="F62" s="38" t="n"/>
-      <c r="G62" s="38" t="n"/>
-      <c r="H62" s="38" t="n"/>
-      <c r="I62" s="38" t="n"/>
+        <v>Quinta</v>
+      </c>
+      <c r="C62" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J62" s="38" t="n"/>
       <c r="K62" s="38" t="n"/>
-      <c r="L62" s="38" t="n"/>
-      <c r="M62" s="38" t="n"/>
-      <c r="N62" s="38" t="n"/>
-      <c r="O62" s="38" t="n"/>
-      <c r="P62" s="38" t="n"/>
-      <c r="Q62" s="38" t="n"/>
+      <c r="L62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q62" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R62" s="38" t="n"/>
       <c r="S62" s="38" t="n"/>
       <c r="T62" s="26">
         <f>IF(A62="","",IFERROR(COUNTIF(D62:K62,"Sim")/(Config!$B$19-COUNTIF(D62:K62,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U62" s="26">
         <f>IF(A62="","",IFERROR(COUNTIF(L62:S62,"Sim")/(Config!$D$19-COUNTIF(L62:S62,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V62" s="24">
         <f>IF(A62="","",MAX(0,Config!$B$19-COUNTIF(D62:K62,"Sim")-COUNTIF(D62:K62,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W62" s="24">
         <f>IF(A62="","",MAX(0,Config!$D$19-COUNTIF(L62:S62,"Sim")-COUNTIF(L62:S62,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X62" s="24">
         <f>IF(A62="","",V62+W62)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y62" s="29">
         <f>IF(OR(A62="",AA62=""),"",LEFT(AA62,LEN(AA62)-2))</f>
@@ -8862,171 +9194,333 @@
       </c>
       <c r="AB62" s="39">
         <f>IF(A62="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A62)+1)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="37" t="n"/>
-      <c r="B63" s="24">
+      <c r="A63" s="37" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B63" s="24" t="str">
         <f>IF(A63="","",CHOOSE(WEEKDAY(A63,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C63" s="38" t="n"/>
-      <c r="D63" s="38" t="n"/>
-      <c r="E63" s="38" t="n"/>
-      <c r="F63" s="38" t="n"/>
-      <c r="G63" s="38" t="n"/>
-      <c r="H63" s="38" t="n"/>
-      <c r="I63" s="38" t="n"/>
+        <v>Sexta</v>
+      </c>
+      <c r="C63" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E63" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="J63" s="38" t="n"/>
       <c r="K63" s="38" t="n"/>
-      <c r="L63" s="38" t="n"/>
-      <c r="M63" s="38" t="n"/>
-      <c r="N63" s="38" t="n"/>
-      <c r="O63" s="38" t="n"/>
-      <c r="P63" s="38" t="n"/>
-      <c r="Q63" s="38" t="n"/>
+      <c r="L63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M63" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="N63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q63" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R63" s="38" t="n"/>
       <c r="S63" s="38" t="n"/>
       <c r="T63" s="26">
         <f>IF(A63="","",IFERROR(COUNTIF(D63:K63,"Sim")/(Config!$B$19-COUNTIF(D63:K63,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="U63" s="26">
         <f>IF(A63="","",IFERROR(COUNTIF(L63:S63,"Sim")/(Config!$D$19-COUNTIF(L63:S63,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V63" s="24">
         <f>IF(A63="","",MAX(0,Config!$B$19-COUNTIF(D63:K63,"Sim")-COUNTIF(D63:K63,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W63" s="24">
         <f>IF(A63="","",MAX(0,Config!$D$19-COUNTIF(L63:S63,"Sim")-COUNTIF(L63:S63,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X63" s="24">
         <f>IF(A63="","",V63+W63)</f>
-        <v/>
-      </c>
-      <c r="Y63" s="29">
+        <v>2</v>
+      </c>
+      <c r="Y63" s="29" t="str">
         <f>IF(OR(A63="",AA63=""),"",LEFT(AA63,LEN(AA63)-2))</f>
-        <v/>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="Z63" s="39">
         <f>IF(OR(A63="",X63=0),0,X63*100000+A63/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA63" s="39">
+        <v>200000.46255</v>
+      </c>
+      <c r="AA63" s="39" t="str">
         <f>IF(A63="","",IF(AND(Config!$B$10&lt;&gt;"",D63&lt;&gt;"Sim",D63&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E63&lt;&gt;"Sim",E63&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F63&lt;&gt;"Sim",F63&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G63&lt;&gt;"Sim",G63&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H63&lt;&gt;"Sim",H63&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I63&lt;&gt;"Sim",I63&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J63&lt;&gt;"Sim",J63&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K63&lt;&gt;"Sim",K63&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L63&lt;&gt;"Sim",L63&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M63&lt;&gt;"Sim",M63&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N63&lt;&gt;"Sim",N63&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O63&lt;&gt;"Sim",O63&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P63&lt;&gt;"Sim",P63&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q63&lt;&gt;"Sim",Q63&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R63&lt;&gt;"Sim",R63&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S63&lt;&gt;"Sim",S63&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Fechamento do dia lançado no Caixa (09); </v>
       </c>
       <c r="AB63" s="39">
         <f>IF(A63="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A63)+1)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="37" t="n"/>
-      <c r="B64" s="24">
+      <c r="A64" s="37" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B64" s="24" t="str">
         <f>IF(A64="","",CHOOSE(WEEKDAY(A64,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C64" s="38" t="n"/>
-      <c r="D64" s="38" t="n"/>
-      <c r="E64" s="38" t="n"/>
-      <c r="F64" s="38" t="n"/>
-      <c r="G64" s="38" t="n"/>
-      <c r="H64" s="38" t="n"/>
-      <c r="I64" s="38" t="n"/>
+        <v>Segunda</v>
+      </c>
+      <c r="C64" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J64" s="38" t="n"/>
       <c r="K64" s="38" t="n"/>
-      <c r="L64" s="38" t="n"/>
-      <c r="M64" s="38" t="n"/>
-      <c r="N64" s="38" t="n"/>
-      <c r="O64" s="38" t="n"/>
-      <c r="P64" s="38" t="n"/>
-      <c r="Q64" s="38" t="n"/>
+      <c r="L64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M64" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="N64" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q64" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R64" s="38" t="n"/>
       <c r="S64" s="38" t="n"/>
       <c r="T64" s="26">
         <f>IF(A64="","",IFERROR(COUNTIF(D64:K64,"Sim")/(Config!$B$19-COUNTIF(D64:K64,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U64" s="26">
         <f>IF(A64="","",IFERROR(COUNTIF(L64:S64,"Sim")/(Config!$D$19-COUNTIF(L64:S64,"N/A")),""))</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="V64" s="24">
         <f>IF(A64="","",MAX(0,Config!$B$19-COUNTIF(D64:K64,"Sim")-COUNTIF(D64:K64,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W64" s="24">
         <f>IF(A64="","",MAX(0,Config!$D$19-COUNTIF(L64:S64,"Sim")-COUNTIF(L64:S64,"N/A")))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="X64" s="24">
         <f>IF(A64="","",V64+W64)</f>
-        <v/>
-      </c>
-      <c r="Y64" s="29">
+        <v>2</v>
+      </c>
+      <c r="Y64" s="29" t="str">
         <f>IF(OR(A64="",AA64=""),"",LEFT(AA64,LEN(AA64)-2))</f>
-        <v/>
+        <v>Fechamento do dia lançado no Caixa (09); Situação de cada horário marcada (realizado, falta, cancelado)</v>
       </c>
       <c r="Z64" s="39">
         <f>IF(OR(A64="",X64=0),0,X64*100000+A64/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA64" s="39">
+        <v>200000.46258</v>
+      </c>
+      <c r="AA64" s="39" t="str">
         <f>IF(A64="","",IF(AND(Config!$B$10&lt;&gt;"",D64&lt;&gt;"Sim",D64&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E64&lt;&gt;"Sim",E64&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F64&lt;&gt;"Sim",F64&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G64&lt;&gt;"Sim",G64&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H64&lt;&gt;"Sim",H64&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I64&lt;&gt;"Sim",I64&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J64&lt;&gt;"Sim",J64&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K64&lt;&gt;"Sim",K64&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L64&lt;&gt;"Sim",L64&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M64&lt;&gt;"Sim",M64&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N64&lt;&gt;"Sim",N64&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O64&lt;&gt;"Sim",O64&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P64&lt;&gt;"Sim",P64&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q64&lt;&gt;"Sim",Q64&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R64&lt;&gt;"Sim",R64&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S64&lt;&gt;"Sim",S64&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Fechamento do dia lançado no Caixa (09); Situação de cada horário marcada (realizado, falta, cancelado); </v>
       </c>
       <c r="AB64" s="39">
         <f>IF(A64="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A64)+1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="37" t="n"/>
-      <c r="B65" s="24">
+      <c r="A65" s="37" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B65" s="24" t="str">
         <f>IF(A65="","",CHOOSE(WEEKDAY(A65,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C65" s="38" t="n"/>
-      <c r="D65" s="38" t="n"/>
-      <c r="E65" s="38" t="n"/>
-      <c r="F65" s="38" t="n"/>
-      <c r="G65" s="38" t="n"/>
-      <c r="H65" s="38" t="n"/>
-      <c r="I65" s="38" t="n"/>
+        <v>Terça</v>
+      </c>
+      <c r="C65" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J65" s="38" t="n"/>
       <c r="K65" s="38" t="n"/>
-      <c r="L65" s="38" t="n"/>
-      <c r="M65" s="38" t="n"/>
-      <c r="N65" s="38" t="n"/>
-      <c r="O65" s="38" t="n"/>
-      <c r="P65" s="38" t="n"/>
-      <c r="Q65" s="38" t="n"/>
+      <c r="L65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q65" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R65" s="38" t="n"/>
       <c r="S65" s="38" t="n"/>
       <c r="T65" s="26">
         <f>IF(A65="","",IFERROR(COUNTIF(D65:K65,"Sim")/(Config!$B$19-COUNTIF(D65:K65,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U65" s="26">
         <f>IF(A65="","",IFERROR(COUNTIF(L65:S65,"Sim")/(Config!$D$19-COUNTIF(L65:S65,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V65" s="24">
         <f>IF(A65="","",MAX(0,Config!$B$19-COUNTIF(D65:K65,"Sim")-COUNTIF(D65:K65,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W65" s="24">
         <f>IF(A65="","",MAX(0,Config!$D$19-COUNTIF(L65:S65,"Sim")-COUNTIF(L65:S65,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X65" s="24">
         <f>IF(A65="","",V65+W65)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y65" s="29">
         <f>IF(OR(A65="",AA65=""),"",LEFT(AA65,LEN(AA65)-2))</f>
@@ -9042,51 +9536,105 @@
       </c>
       <c r="AB65" s="39">
         <f>IF(A65="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A65)+1)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="37" t="n"/>
-      <c r="B66" s="24">
+      <c r="A66" s="37" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B66" s="24" t="str">
         <f>IF(A66="","",CHOOSE(WEEKDAY(A66,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C66" s="38" t="n"/>
-      <c r="D66" s="38" t="n"/>
-      <c r="E66" s="38" t="n"/>
-      <c r="F66" s="38" t="n"/>
-      <c r="G66" s="38" t="n"/>
-      <c r="H66" s="38" t="n"/>
-      <c r="I66" s="38" t="n"/>
+        <v>Quarta</v>
+      </c>
+      <c r="C66" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J66" s="38" t="n"/>
       <c r="K66" s="38" t="n"/>
-      <c r="L66" s="38" t="n"/>
-      <c r="M66" s="38" t="n"/>
-      <c r="N66" s="38" t="n"/>
-      <c r="O66" s="38" t="n"/>
-      <c r="P66" s="38" t="n"/>
-      <c r="Q66" s="38" t="n"/>
+      <c r="L66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q66" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R66" s="38" t="n"/>
       <c r="S66" s="38" t="n"/>
       <c r="T66" s="26">
         <f>IF(A66="","",IFERROR(COUNTIF(D66:K66,"Sim")/(Config!$B$19-COUNTIF(D66:K66,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U66" s="26">
         <f>IF(A66="","",IFERROR(COUNTIF(L66:S66,"Sim")/(Config!$D$19-COUNTIF(L66:S66,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V66" s="24">
         <f>IF(A66="","",MAX(0,Config!$B$19-COUNTIF(D66:K66,"Sim")-COUNTIF(D66:K66,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W66" s="24">
         <f>IF(A66="","",MAX(0,Config!$D$19-COUNTIF(L66:S66,"Sim")-COUNTIF(L66:S66,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X66" s="24">
         <f>IF(A66="","",V66+W66)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y66" s="29">
         <f>IF(OR(A66="",AA66=""),"",LEFT(AA66,LEN(AA66)-2))</f>
@@ -9102,51 +9650,105 @@
       </c>
       <c r="AB66" s="39">
         <f>IF(A66="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A66)+1)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="37" t="n"/>
-      <c r="B67" s="24">
+      <c r="A67" s="37" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B67" s="24" t="str">
         <f>IF(A67="","",CHOOSE(WEEKDAY(A67,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C67" s="38" t="n"/>
-      <c r="D67" s="38" t="n"/>
-      <c r="E67" s="38" t="n"/>
-      <c r="F67" s="38" t="n"/>
-      <c r="G67" s="38" t="n"/>
-      <c r="H67" s="38" t="n"/>
-      <c r="I67" s="38" t="n"/>
+        <v>Quinta</v>
+      </c>
+      <c r="C67" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J67" s="38" t="n"/>
       <c r="K67" s="38" t="n"/>
-      <c r="L67" s="38" t="n"/>
-      <c r="M67" s="38" t="n"/>
-      <c r="N67" s="38" t="n"/>
-      <c r="O67" s="38" t="n"/>
-      <c r="P67" s="38" t="n"/>
-      <c r="Q67" s="38" t="n"/>
+      <c r="L67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q67" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R67" s="38" t="n"/>
       <c r="S67" s="38" t="n"/>
       <c r="T67" s="26">
         <f>IF(A67="","",IFERROR(COUNTIF(D67:K67,"Sim")/(Config!$B$19-COUNTIF(D67:K67,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U67" s="26">
         <f>IF(A67="","",IFERROR(COUNTIF(L67:S67,"Sim")/(Config!$D$19-COUNTIF(L67:S67,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V67" s="24">
         <f>IF(A67="","",MAX(0,Config!$B$19-COUNTIF(D67:K67,"Sim")-COUNTIF(D67:K67,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W67" s="24">
         <f>IF(A67="","",MAX(0,Config!$D$19-COUNTIF(L67:S67,"Sim")-COUNTIF(L67:S67,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X67" s="24">
         <f>IF(A67="","",V67+W67)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y67" s="29">
         <f>IF(OR(A67="",AA67=""),"",LEFT(AA67,LEN(AA67)-2))</f>
@@ -9162,51 +9764,105 @@
       </c>
       <c r="AB67" s="39">
         <f>IF(A67="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A67)+1)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="37" t="n"/>
-      <c r="B68" s="24">
+      <c r="A68" s="37" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B68" s="24" t="str">
         <f>IF(A68="","",CHOOSE(WEEKDAY(A68,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C68" s="38" t="n"/>
-      <c r="D68" s="38" t="n"/>
-      <c r="E68" s="38" t="n"/>
-      <c r="F68" s="38" t="n"/>
-      <c r="G68" s="38" t="n"/>
-      <c r="H68" s="38" t="n"/>
-      <c r="I68" s="38" t="n"/>
+        <v>Sexta</v>
+      </c>
+      <c r="C68" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="J68" s="38" t="n"/>
       <c r="K68" s="38" t="n"/>
-      <c r="L68" s="38" t="n"/>
-      <c r="M68" s="38" t="n"/>
-      <c r="N68" s="38" t="n"/>
-      <c r="O68" s="38" t="n"/>
-      <c r="P68" s="38" t="n"/>
-      <c r="Q68" s="38" t="n"/>
+      <c r="L68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q68" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R68" s="38" t="n"/>
       <c r="S68" s="38" t="n"/>
       <c r="T68" s="26">
         <f>IF(A68="","",IFERROR(COUNTIF(D68:K68,"Sim")/(Config!$B$19-COUNTIF(D68:K68,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U68" s="26">
         <f>IF(A68="","",IFERROR(COUNTIF(L68:S68,"Sim")/(Config!$D$19-COUNTIF(L68:S68,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V68" s="24">
         <f>IF(A68="","",MAX(0,Config!$B$19-COUNTIF(D68:K68,"Sim")-COUNTIF(D68:K68,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W68" s="24">
         <f>IF(A68="","",MAX(0,Config!$D$19-COUNTIF(L68:S68,"Sim")-COUNTIF(L68:S68,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X68" s="24">
         <f>IF(A68="","",V68+W68)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y68" s="29">
         <f>IF(OR(A68="",AA68=""),"",LEFT(AA68,LEN(AA68)-2))</f>
@@ -9222,51 +9878,105 @@
       </c>
       <c r="AB68" s="39">
         <f>IF(A68="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A68)+1)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="37" t="n"/>
-      <c r="B69" s="24">
+      <c r="A69" s="37" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B69" s="24" t="str">
         <f>IF(A69="","",CHOOSE(WEEKDAY(A69,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C69" s="38" t="n"/>
-      <c r="D69" s="38" t="n"/>
-      <c r="E69" s="38" t="n"/>
-      <c r="F69" s="38" t="n"/>
-      <c r="G69" s="38" t="n"/>
-      <c r="H69" s="38" t="n"/>
-      <c r="I69" s="38" t="n"/>
+        <v>Segunda</v>
+      </c>
+      <c r="C69" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J69" s="38" t="n"/>
       <c r="K69" s="38" t="n"/>
-      <c r="L69" s="38" t="n"/>
-      <c r="M69" s="38" t="n"/>
-      <c r="N69" s="38" t="n"/>
-      <c r="O69" s="38" t="n"/>
-      <c r="P69" s="38" t="n"/>
-      <c r="Q69" s="38" t="n"/>
+      <c r="L69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q69" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R69" s="38" t="n"/>
       <c r="S69" s="38" t="n"/>
       <c r="T69" s="26">
         <f>IF(A69="","",IFERROR(COUNTIF(D69:K69,"Sim")/(Config!$B$19-COUNTIF(D69:K69,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U69" s="26">
         <f>IF(A69="","",IFERROR(COUNTIF(L69:S69,"Sim")/(Config!$D$19-COUNTIF(L69:S69,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V69" s="24">
         <f>IF(A69="","",MAX(0,Config!$B$19-COUNTIF(D69:K69,"Sim")-COUNTIF(D69:K69,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W69" s="24">
         <f>IF(A69="","",MAX(0,Config!$D$19-COUNTIF(L69:S69,"Sim")-COUNTIF(L69:S69,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X69" s="24">
         <f>IF(A69="","",V69+W69)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y69" s="29">
         <f>IF(OR(A69="",AA69=""),"",LEFT(AA69,LEN(AA69)-2))</f>
@@ -9282,111 +9992,219 @@
       </c>
       <c r="AB69" s="39">
         <f>IF(A69="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A69)+1)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="37" t="n"/>
-      <c r="B70" s="24">
+      <c r="A70" s="37" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" s="24" t="str">
         <f>IF(A70="","",CHOOSE(WEEKDAY(A70,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C70" s="38" t="n"/>
-      <c r="D70" s="38" t="n"/>
-      <c r="E70" s="38" t="n"/>
-      <c r="F70" s="38" t="n"/>
-      <c r="G70" s="38" t="n"/>
-      <c r="H70" s="38" t="n"/>
-      <c r="I70" s="38" t="n"/>
+        <v>Terça</v>
+      </c>
+      <c r="C70" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J70" s="38" t="n"/>
       <c r="K70" s="38" t="n"/>
-      <c r="L70" s="38" t="n"/>
-      <c r="M70" s="38" t="n"/>
-      <c r="N70" s="38" t="n"/>
-      <c r="O70" s="38" t="n"/>
-      <c r="P70" s="38" t="n"/>
-      <c r="Q70" s="38" t="n"/>
+      <c r="L70" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M70" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="N70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O70" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q70" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R70" s="38" t="n"/>
       <c r="S70" s="38" t="n"/>
       <c r="T70" s="26">
         <f>IF(A70="","",IFERROR(COUNTIF(D70:K70,"Sim")/(Config!$B$19-COUNTIF(D70:K70,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U70" s="26">
         <f>IF(A70="","",IFERROR(COUNTIF(L70:S70,"Sim")/(Config!$D$19-COUNTIF(L70:S70,"N/A")),""))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="V70" s="24">
         <f>IF(A70="","",MAX(0,Config!$B$19-COUNTIF(D70:K70,"Sim")-COUNTIF(D70:K70,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W70" s="24">
         <f>IF(A70="","",MAX(0,Config!$D$19-COUNTIF(L70:S70,"Sim")-COUNTIF(L70:S70,"N/A")))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="X70" s="24">
         <f>IF(A70="","",V70+W70)</f>
-        <v/>
-      </c>
-      <c r="Y70" s="29">
+        <v>3</v>
+      </c>
+      <c r="Y70" s="29" t="str">
         <f>IF(OR(A70="",AA70=""),"",LEFT(AA70,LEN(AA70)-2))</f>
-        <v/>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Fechamento do dia lançado no Caixa (09); Guias do dia conferidas e guardadas para o lote (13)</v>
       </c>
       <c r="Z70" s="39">
         <f>IF(OR(A70="",X70=0),0,X70*100000+A70/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA70" s="39">
+        <v>300000.46266</v>
+      </c>
+      <c r="AA70" s="39" t="str">
         <f>IF(A70="","",IF(AND(Config!$B$10&lt;&gt;"",D70&lt;&gt;"Sim",D70&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E70&lt;&gt;"Sim",E70&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F70&lt;&gt;"Sim",F70&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G70&lt;&gt;"Sim",G70&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H70&lt;&gt;"Sim",H70&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I70&lt;&gt;"Sim",I70&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J70&lt;&gt;"Sim",J70&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K70&lt;&gt;"Sim",K70&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L70&lt;&gt;"Sim",L70&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M70&lt;&gt;"Sim",M70&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N70&lt;&gt;"Sim",N70&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O70&lt;&gt;"Sim",O70&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P70&lt;&gt;"Sim",P70&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q70&lt;&gt;"Sim",Q70&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R70&lt;&gt;"Sim",R70&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S70&lt;&gt;"Sim",S70&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Caixa do dia fechado e conferido (Pix, cartão, dinheiro); Fechamento do dia lançado no Caixa (09); Guias do dia conferidas e guardadas para o lote (13); </v>
       </c>
       <c r="AB70" s="39">
         <f>IF(A70="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A70)+1)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="37" t="n"/>
-      <c r="B71" s="24">
+      <c r="A71" s="37" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B71" s="24" t="str">
         <f>IF(A71="","",CHOOSE(WEEKDAY(A71,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C71" s="38" t="n"/>
-      <c r="D71" s="38" t="n"/>
-      <c r="E71" s="38" t="n"/>
-      <c r="F71" s="38" t="n"/>
-      <c r="G71" s="38" t="n"/>
-      <c r="H71" s="38" t="n"/>
-      <c r="I71" s="38" t="n"/>
+        <v>Quarta</v>
+      </c>
+      <c r="C71" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J71" s="38" t="n"/>
       <c r="K71" s="38" t="n"/>
-      <c r="L71" s="38" t="n"/>
-      <c r="M71" s="38" t="n"/>
-      <c r="N71" s="38" t="n"/>
-      <c r="O71" s="38" t="n"/>
-      <c r="P71" s="38" t="n"/>
-      <c r="Q71" s="38" t="n"/>
+      <c r="L71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q71" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R71" s="38" t="n"/>
       <c r="S71" s="38" t="n"/>
       <c r="T71" s="26">
         <f>IF(A71="","",IFERROR(COUNTIF(D71:K71,"Sim")/(Config!$B$19-COUNTIF(D71:K71,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U71" s="26">
         <f>IF(A71="","",IFERROR(COUNTIF(L71:S71,"Sim")/(Config!$D$19-COUNTIF(L71:S71,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V71" s="24">
         <f>IF(A71="","",MAX(0,Config!$B$19-COUNTIF(D71:K71,"Sim")-COUNTIF(D71:K71,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W71" s="24">
         <f>IF(A71="","",MAX(0,Config!$D$19-COUNTIF(L71:S71,"Sim")-COUNTIF(L71:S71,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X71" s="24">
         <f>IF(A71="","",V71+W71)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y71" s="29">
         <f>IF(OR(A71="",AA71=""),"",LEFT(AA71,LEN(AA71)-2))</f>
@@ -9402,171 +10220,333 @@
       </c>
       <c r="AB71" s="39">
         <f>IF(A71="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A71)+1)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="37" t="n"/>
-      <c r="B72" s="24">
+      <c r="A72" s="37" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B72" s="24" t="str">
         <f>IF(A72="","",CHOOSE(WEEKDAY(A72,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C72" s="38" t="n"/>
-      <c r="D72" s="38" t="n"/>
-      <c r="E72" s="38" t="n"/>
-      <c r="F72" s="38" t="n"/>
-      <c r="G72" s="38" t="n"/>
-      <c r="H72" s="38" t="n"/>
-      <c r="I72" s="38" t="n"/>
+        <v>Quinta</v>
+      </c>
+      <c r="C72" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E72" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J72" s="38" t="n"/>
       <c r="K72" s="38" t="n"/>
-      <c r="L72" s="38" t="n"/>
-      <c r="M72" s="38" t="n"/>
-      <c r="N72" s="38" t="n"/>
-      <c r="O72" s="38" t="n"/>
-      <c r="P72" s="38" t="n"/>
-      <c r="Q72" s="38" t="n"/>
+      <c r="L72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P72" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q72" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="R72" s="38" t="n"/>
       <c r="S72" s="38" t="n"/>
       <c r="T72" s="26">
         <f>IF(A72="","",IFERROR(COUNTIF(D72:K72,"Sim")/(Config!$B$19-COUNTIF(D72:K72,"N/A")),""))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="U72" s="26">
         <f>IF(A72="","",IFERROR(COUNTIF(L72:S72,"Sim")/(Config!$D$19-COUNTIF(L72:S72,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V72" s="24">
         <f>IF(A72="","",MAX(0,Config!$B$19-COUNTIF(D72:K72,"Sim")-COUNTIF(D72:K72,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W72" s="24">
         <f>IF(A72="","",MAX(0,Config!$D$19-COUNTIF(L72:S72,"Sim")-COUNTIF(L72:S72,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X72" s="24">
         <f>IF(A72="","",V72+W72)</f>
-        <v/>
-      </c>
-      <c r="Y72" s="29">
+        <v>2</v>
+      </c>
+      <c r="Y72" s="29" t="str">
         <f>IF(OR(A72="",AA72=""),"",LEFT(AA72,LEN(AA72)-2))</f>
-        <v/>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Agenda de amanhã revisada e confirmações enviadas</v>
       </c>
       <c r="Z72" s="39">
         <f>IF(OR(A72="",X72=0),0,X72*100000+A72/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA72" s="39">
+        <v>200000.46268</v>
+      </c>
+      <c r="AA72" s="39" t="str">
         <f>IF(A72="","",IF(AND(Config!$B$10&lt;&gt;"",D72&lt;&gt;"Sim",D72&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E72&lt;&gt;"Sim",E72&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F72&lt;&gt;"Sim",F72&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G72&lt;&gt;"Sim",G72&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H72&lt;&gt;"Sim",H72&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I72&lt;&gt;"Sim",I72&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J72&lt;&gt;"Sim",J72&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K72&lt;&gt;"Sim",K72&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L72&lt;&gt;"Sim",L72&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M72&lt;&gt;"Sim",M72&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N72&lt;&gt;"Sim",N72&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O72&lt;&gt;"Sim",O72&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P72&lt;&gt;"Sim",P72&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q72&lt;&gt;"Sim",Q72&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R72&lt;&gt;"Sim",R72&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S72&lt;&gt;"Sim",S72&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Faltas e cancelamentos de ontem registrados na agenda; Agenda de amanhã revisada e confirmações enviadas; </v>
       </c>
       <c r="AB72" s="39">
         <f>IF(A72="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A72)+1)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="37" t="n"/>
-      <c r="B73" s="24">
+      <c r="A73" s="37" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B73" s="24" t="str">
         <f>IF(A73="","",CHOOSE(WEEKDAY(A73,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C73" s="38" t="n"/>
-      <c r="D73" s="38" t="n"/>
-      <c r="E73" s="38" t="n"/>
-      <c r="F73" s="38" t="n"/>
-      <c r="G73" s="38" t="n"/>
-      <c r="H73" s="38" t="n"/>
-      <c r="I73" s="38" t="n"/>
+        <v>Sexta</v>
+      </c>
+      <c r="C73" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="J73" s="38" t="n"/>
       <c r="K73" s="38" t="n"/>
-      <c r="L73" s="38" t="n"/>
-      <c r="M73" s="38" t="n"/>
-      <c r="N73" s="38" t="n"/>
-      <c r="O73" s="38" t="n"/>
-      <c r="P73" s="38" t="n"/>
-      <c r="Q73" s="38" t="n"/>
+      <c r="L73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P73" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q73" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="R73" s="38" t="n"/>
       <c r="S73" s="38" t="n"/>
       <c r="T73" s="26">
         <f>IF(A73="","",IFERROR(COUNTIF(D73:K73,"Sim")/(Config!$B$19-COUNTIF(D73:K73,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U73" s="26">
         <f>IF(A73="","",IFERROR(COUNTIF(L73:S73,"Sim")/(Config!$D$19-COUNTIF(L73:S73,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V73" s="24">
         <f>IF(A73="","",MAX(0,Config!$B$19-COUNTIF(D73:K73,"Sim")-COUNTIF(D73:K73,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W73" s="24">
         <f>IF(A73="","",MAX(0,Config!$D$19-COUNTIF(L73:S73,"Sim")-COUNTIF(L73:S73,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X73" s="24">
         <f>IF(A73="","",V73+W73)</f>
-        <v/>
-      </c>
-      <c r="Y73" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y73" s="29" t="str">
         <f>IF(OR(A73="",AA73=""),"",LEFT(AA73,LEN(AA73)-2))</f>
-        <v/>
+        <v>Agenda de amanhã revisada e confirmações enviadas</v>
       </c>
       <c r="Z73" s="39">
         <f>IF(OR(A73="",X73=0),0,X73*100000+A73/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="39">
+        <v>100000.46269</v>
+      </c>
+      <c r="AA73" s="39" t="str">
         <f>IF(A73="","",IF(AND(Config!$B$10&lt;&gt;"",D73&lt;&gt;"Sim",D73&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E73&lt;&gt;"Sim",E73&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F73&lt;&gt;"Sim",F73&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G73&lt;&gt;"Sim",G73&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H73&lt;&gt;"Sim",H73&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I73&lt;&gt;"Sim",I73&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J73&lt;&gt;"Sim",J73&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K73&lt;&gt;"Sim",K73&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L73&lt;&gt;"Sim",L73&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M73&lt;&gt;"Sim",M73&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N73&lt;&gt;"Sim",N73&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O73&lt;&gt;"Sim",O73&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P73&lt;&gt;"Sim",P73&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q73&lt;&gt;"Sim",Q73&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R73&lt;&gt;"Sim",R73&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S73&lt;&gt;"Sim",S73&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Agenda de amanhã revisada e confirmações enviadas; </v>
       </c>
       <c r="AB73" s="39">
         <f>IF(A73="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A73)+1)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="37" t="n"/>
-      <c r="B74" s="24">
+      <c r="A74" s="37" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B74" s="24" t="str">
         <f>IF(A74="","",CHOOSE(WEEKDAY(A74,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C74" s="38" t="n"/>
-      <c r="D74" s="38" t="n"/>
-      <c r="E74" s="38" t="n"/>
-      <c r="F74" s="38" t="n"/>
-      <c r="G74" s="38" t="n"/>
-      <c r="H74" s="38" t="n"/>
-      <c r="I74" s="38" t="n"/>
+        <v>Terça</v>
+      </c>
+      <c r="C74" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J74" s="38" t="n"/>
       <c r="K74" s="38" t="n"/>
-      <c r="L74" s="38" t="n"/>
-      <c r="M74" s="38" t="n"/>
-      <c r="N74" s="38" t="n"/>
-      <c r="O74" s="38" t="n"/>
-      <c r="P74" s="38" t="n"/>
-      <c r="Q74" s="38" t="n"/>
+      <c r="L74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q74" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R74" s="38" t="n"/>
       <c r="S74" s="38" t="n"/>
       <c r="T74" s="26">
         <f>IF(A74="","",IFERROR(COUNTIF(D74:K74,"Sim")/(Config!$B$19-COUNTIF(D74:K74,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U74" s="26">
         <f>IF(A74="","",IFERROR(COUNTIF(L74:S74,"Sim")/(Config!$D$19-COUNTIF(L74:S74,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V74" s="24">
         <f>IF(A74="","",MAX(0,Config!$B$19-COUNTIF(D74:K74,"Sim")-COUNTIF(D74:K74,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W74" s="24">
         <f>IF(A74="","",MAX(0,Config!$D$19-COUNTIF(L74:S74,"Sim")-COUNTIF(L74:S74,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X74" s="24">
         <f>IF(A74="","",V74+W74)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y74" s="29">
         <f>IF(OR(A74="",AA74=""),"",LEFT(AA74,LEN(AA74)-2))</f>
@@ -9582,51 +10562,105 @@
       </c>
       <c r="AB74" s="39">
         <f>IF(A74="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A74)+1)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="37" t="n"/>
-      <c r="B75" s="24">
+      <c r="A75" s="37" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B75" s="24" t="str">
         <f>IF(A75="","",CHOOSE(WEEKDAY(A75,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C75" s="38" t="n"/>
-      <c r="D75" s="38" t="n"/>
-      <c r="E75" s="38" t="n"/>
-      <c r="F75" s="38" t="n"/>
-      <c r="G75" s="38" t="n"/>
-      <c r="H75" s="38" t="n"/>
-      <c r="I75" s="38" t="n"/>
+        <v>Quarta</v>
+      </c>
+      <c r="C75" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J75" s="38" t="n"/>
       <c r="K75" s="38" t="n"/>
-      <c r="L75" s="38" t="n"/>
-      <c r="M75" s="38" t="n"/>
-      <c r="N75" s="38" t="n"/>
-      <c r="O75" s="38" t="n"/>
-      <c r="P75" s="38" t="n"/>
-      <c r="Q75" s="38" t="n"/>
+      <c r="L75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q75" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R75" s="38" t="n"/>
       <c r="S75" s="38" t="n"/>
       <c r="T75" s="26">
         <f>IF(A75="","",IFERROR(COUNTIF(D75:K75,"Sim")/(Config!$B$19-COUNTIF(D75:K75,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U75" s="26">
         <f>IF(A75="","",IFERROR(COUNTIF(L75:S75,"Sim")/(Config!$D$19-COUNTIF(L75:S75,"N/A")),""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V75" s="24">
         <f>IF(A75="","",MAX(0,Config!$B$19-COUNTIF(D75:K75,"Sim")-COUNTIF(D75:K75,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W75" s="24">
         <f>IF(A75="","",MAX(0,Config!$D$19-COUNTIF(L75:S75,"Sim")-COUNTIF(L75:S75,"N/A")))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X75" s="24">
         <f>IF(A75="","",V75+W75)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y75" s="29">
         <f>IF(OR(A75="",AA75=""),"",LEFT(AA75,LEN(AA75)-2))</f>
@@ -9642,127 +10676,227 @@
       </c>
       <c r="AB75" s="39">
         <f>IF(A75="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A75)+1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="37" t="n"/>
-      <c r="B76" s="24">
+      <c r="A76" s="37" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B76" s="24" t="str">
         <f>IF(A76="","",CHOOSE(WEEKDAY(A76,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C76" s="38" t="n"/>
-      <c r="D76" s="38" t="n"/>
-      <c r="E76" s="38" t="n"/>
-      <c r="F76" s="38" t="n"/>
-      <c r="G76" s="38" t="n"/>
-      <c r="H76" s="38" t="n"/>
-      <c r="I76" s="38" t="n"/>
+        <v>Quinta</v>
+      </c>
+      <c r="C76" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G76" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J76" s="38" t="n"/>
       <c r="K76" s="38" t="n"/>
-      <c r="L76" s="38" t="n"/>
+      <c r="L76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="M76" s="38" t="n"/>
-      <c r="N76" s="38" t="n"/>
-      <c r="O76" s="38" t="n"/>
-      <c r="P76" s="38" t="n"/>
-      <c r="Q76" s="38" t="n"/>
+      <c r="N76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q76" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R76" s="38" t="n"/>
       <c r="S76" s="38" t="n"/>
       <c r="T76" s="26">
         <f>IF(A76="","",IFERROR(COUNTIF(D76:K76,"Sim")/(Config!$B$19-COUNTIF(D76:K76,"N/A")),""))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="U76" s="26">
         <f>IF(A76="","",IFERROR(COUNTIF(L76:S76,"Sim")/(Config!$D$19-COUNTIF(L76:S76,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V76" s="24">
         <f>IF(A76="","",MAX(0,Config!$B$19-COUNTIF(D76:K76,"Sim")-COUNTIF(D76:K76,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W76" s="24">
         <f>IF(A76="","",MAX(0,Config!$D$19-COUNTIF(L76:S76,"Sim")-COUNTIF(L76:S76,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X76" s="24">
         <f>IF(A76="","",V76+W76)</f>
-        <v/>
-      </c>
-      <c r="Y76" s="29">
+        <v>2</v>
+      </c>
+      <c r="Y76" s="29" t="str">
         <f>IF(OR(A76="",AA76=""),"",LEFT(AA76,LEN(AA76)-2))</f>
-        <v/>
+        <v>Guias e autorizações de convênio do dia separadas; Fechamento do dia lançado no Caixa (09)</v>
       </c>
       <c r="Z76" s="39">
         <f>IF(OR(A76="",X76=0),0,X76*100000+A76/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA76" s="39">
+        <v>200000.46275</v>
+      </c>
+      <c r="AA76" s="39" t="str">
         <f>IF(A76="","",IF(AND(Config!$B$10&lt;&gt;"",D76&lt;&gt;"Sim",D76&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E76&lt;&gt;"Sim",E76&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F76&lt;&gt;"Sim",F76&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G76&lt;&gt;"Sim",G76&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H76&lt;&gt;"Sim",H76&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I76&lt;&gt;"Sim",I76&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J76&lt;&gt;"Sim",J76&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K76&lt;&gt;"Sim",K76&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L76&lt;&gt;"Sim",L76&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M76&lt;&gt;"Sim",M76&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N76&lt;&gt;"Sim",N76&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O76&lt;&gt;"Sim",O76&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P76&lt;&gt;"Sim",P76&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q76&lt;&gt;"Sim",Q76&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R76&lt;&gt;"Sim",R76&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S76&lt;&gt;"Sim",S76&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Guias e autorizações de convênio do dia separadas; Fechamento do dia lançado no Caixa (09); </v>
       </c>
       <c r="AB76" s="39">
         <f>IF(A76="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A76)+1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="37" t="n"/>
-      <c r="B77" s="24">
+      <c r="A77" s="37" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B77" s="24" t="str">
         <f>IF(A77="","",CHOOSE(WEEKDAY(A77,2),"Segunda","Terça","Quarta","Quinta","Sexta","Sábado","Domingo"))</f>
-        <v/>
-      </c>
-      <c r="C77" s="38" t="n"/>
-      <c r="D77" s="38" t="n"/>
-      <c r="E77" s="38" t="n"/>
-      <c r="F77" s="38" t="n"/>
-      <c r="G77" s="38" t="n"/>
-      <c r="H77" s="38" t="n"/>
-      <c r="I77" s="38" t="n"/>
+        <v>Sexta</v>
+      </c>
+      <c r="C77" s="38" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho</t>
+        </is>
+      </c>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H77" s="38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="J77" s="38" t="n"/>
       <c r="K77" s="38" t="n"/>
-      <c r="L77" s="38" t="n"/>
-      <c r="M77" s="38" t="n"/>
-      <c r="N77" s="38" t="n"/>
+      <c r="L77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="O77" s="38" t="n"/>
-      <c r="P77" s="38" t="n"/>
-      <c r="Q77" s="38" t="n"/>
+      <c r="P77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q77" s="38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="R77" s="38" t="n"/>
       <c r="S77" s="38" t="n"/>
       <c r="T77" s="26">
         <f>IF(A77="","",IFERROR(COUNTIF(D77:K77,"Sim")/(Config!$B$19-COUNTIF(D77:K77,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="U77" s="26">
         <f>IF(A77="","",IFERROR(COUNTIF(L77:S77,"Sim")/(Config!$D$19-COUNTIF(L77:S77,"N/A")),""))</f>
-        <v/>
+        <v>0.833333333333333</v>
       </c>
       <c r="V77" s="24">
         <f>IF(A77="","",MAX(0,Config!$B$19-COUNTIF(D77:K77,"Sim")-COUNTIF(D77:K77,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W77" s="24">
         <f>IF(A77="","",MAX(0,Config!$D$19-COUNTIF(L77:S77,"Sim")-COUNTIF(L77:S77,"N/A")))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X77" s="24">
         <f>IF(A77="","",V77+W77)</f>
-        <v/>
-      </c>
-      <c r="Y77" s="29">
+        <v>2</v>
+      </c>
+      <c r="Y77" s="29" t="str">
         <f>IF(OR(A77="",AA77=""),"",LEFT(AA77,LEN(AA77)-2))</f>
-        <v/>
+        <v>Troco e maquininha conferidos; Guias do dia conferidas e guardadas para o lote (13)</v>
       </c>
       <c r="Z77" s="39">
         <f>IF(OR(A77="",X77=0),0,X77*100000+A77/100000)</f>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="39">
+        <v>200000.46276</v>
+      </c>
+      <c r="AA77" s="39" t="str">
         <f>IF(A77="","",IF(AND(Config!$B$10&lt;&gt;"",D77&lt;&gt;"Sim",D77&lt;&gt;"N/A"),Config!$B$10&amp;"; ","")&amp;IF(AND(Config!$B$11&lt;&gt;"",E77&lt;&gt;"Sim",E77&lt;&gt;"N/A"),Config!$B$11&amp;"; ","")&amp;IF(AND(Config!$B$12&lt;&gt;"",F77&lt;&gt;"Sim",F77&lt;&gt;"N/A"),Config!$B$12&amp;"; ","")&amp;IF(AND(Config!$B$13&lt;&gt;"",G77&lt;&gt;"Sim",G77&lt;&gt;"N/A"),Config!$B$13&amp;"; ","")&amp;IF(AND(Config!$B$14&lt;&gt;"",H77&lt;&gt;"Sim",H77&lt;&gt;"N/A"),Config!$B$14&amp;"; ","")&amp;IF(AND(Config!$B$15&lt;&gt;"",I77&lt;&gt;"Sim",I77&lt;&gt;"N/A"),Config!$B$15&amp;"; ","")&amp;IF(AND(Config!$B$16&lt;&gt;"",J77&lt;&gt;"Sim",J77&lt;&gt;"N/A"),Config!$B$16&amp;"; ","")&amp;IF(AND(Config!$B$17&lt;&gt;"",K77&lt;&gt;"Sim",K77&lt;&gt;"N/A"),Config!$B$17&amp;"; ","")&amp;IF(AND(Config!$D$10&lt;&gt;"",L77&lt;&gt;"Sim",L77&lt;&gt;"N/A"),Config!$D$10&amp;"; ","")&amp;IF(AND(Config!$D$11&lt;&gt;"",M77&lt;&gt;"Sim",M77&lt;&gt;"N/A"),Config!$D$11&amp;"; ","")&amp;IF(AND(Config!$D$12&lt;&gt;"",N77&lt;&gt;"Sim",N77&lt;&gt;"N/A"),Config!$D$12&amp;"; ","")&amp;IF(AND(Config!$D$13&lt;&gt;"",O77&lt;&gt;"Sim",O77&lt;&gt;"N/A"),Config!$D$13&amp;"; ","")&amp;IF(AND(Config!$D$14&lt;&gt;"",P77&lt;&gt;"Sim",P77&lt;&gt;"N/A"),Config!$D$14&amp;"; ","")&amp;IF(AND(Config!$D$15&lt;&gt;"",Q77&lt;&gt;"Sim",Q77&lt;&gt;"N/A"),Config!$D$15&amp;"; ","")&amp;IF(AND(Config!$D$16&lt;&gt;"",R77&lt;&gt;"Sim",R77&lt;&gt;"N/A"),Config!$D$16&amp;"; ","")&amp;IF(AND(Config!$D$17&lt;&gt;"",S77&lt;&gt;"Sim",S77&lt;&gt;"N/A"),Config!$D$17&amp;"; ",""))</f>
-        <v/>
+        <v>Troco e maquininha conferidos; Guias do dia conferidas e guardadas para o lote (13); </v>
       </c>
       <c r="AB77" s="39">
         <f>IF(A77="",0,COUNTIF($A$5:$A$304,"&gt;"&amp;A77)+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -300,7 +301,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -317,7 +318,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -333,7 +334,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -755,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -928,17 +929,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2219,9 +2232,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="32">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="32" t="n">
+        <v>46279</v>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -24562,13 +24562,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$10,0,0,MAX(1,COUNTA(Config!$F$10:$F$19)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="D5:S304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>Deixe =HOJE() para acompanhar o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -986,7 +986,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
-        <f>Config!$B$4&amp;" · Abertura e fechamento do dia · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
+        <f>Config!$B$4&amp;" · Abertura e fechamento do dia · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
         <v>Clínica Vida Plena (exemplo fictício) · Abertura e fechamento do dia · 14/09/2026</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/04-checklist-do-dia.xlsx
@@ -777,6 +777,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -917,7 +918,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
